--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBFCC801-7209-4D4D-A20F-6691C435F746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3D35629-E86E-4495-9CD0-347BC84A87DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="186">
   <si>
     <t>date</t>
   </si>
@@ -589,6 +589,15 @@
   <si>
     <t>Sun 20 September, 20:15</t>
   </si>
+  <si>
+    <t>Fri 9 October, 18:00</t>
+  </si>
+  <si>
+    <t>Fri 9 October, 20:30</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 14:45</t>
+  </si>
 </sst>
 </file>
 
@@ -643,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -661,6 +670,10 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -995,11 +1008,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ79"/>
+  <dimension ref="A1:CJ82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
@@ -1330,7 +1343,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H79" si="0">100-G2</f>
+        <f t="shared" ref="H2:H82" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -22001,6 +22014,798 @@
         <v>0</v>
       </c>
       <c r="CJ79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:88" ht="30">
+      <c r="B80" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" t="s">
+        <v>105</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>49</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="I80">
+        <v>1.83</v>
+      </c>
+      <c r="J80">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K80">
+        <v>15</v>
+      </c>
+      <c r="L80">
+        <v>11</v>
+      </c>
+      <c r="M80">
+        <v>6</v>
+      </c>
+      <c r="N80">
+        <v>2</v>
+      </c>
+      <c r="O80">
+        <v>3</v>
+      </c>
+      <c r="P80">
+        <v>4</v>
+      </c>
+      <c r="Q80">
+        <v>3</v>
+      </c>
+      <c r="R80">
+        <v>4</v>
+      </c>
+      <c r="S80">
+        <v>441</v>
+      </c>
+      <c r="T80">
+        <v>457</v>
+      </c>
+      <c r="U80">
+        <v>16</v>
+      </c>
+      <c r="V80">
+        <v>5</v>
+      </c>
+      <c r="W80">
+        <v>6</v>
+      </c>
+      <c r="X80">
+        <v>7</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA80">
+        <v>5</v>
+      </c>
+      <c r="AB80">
+        <v>7</v>
+      </c>
+      <c r="AC80">
+        <v>4</v>
+      </c>
+      <c r="AD80">
+        <v>2</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>11</v>
+      </c>
+      <c r="AH80">
+        <v>7</v>
+      </c>
+      <c r="AI80">
+        <v>4</v>
+      </c>
+      <c r="AJ80">
+        <v>4</v>
+      </c>
+      <c r="AK80">
+        <v>1.48</v>
+      </c>
+      <c r="AL80">
+        <v>0.41</v>
+      </c>
+      <c r="AM80">
+        <v>0.35</v>
+      </c>
+      <c r="AN80">
+        <v>0.17</v>
+      </c>
+      <c r="AO80">
+        <v>1.83</v>
+      </c>
+      <c r="AP80">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AQ80">
+        <v>2.37</v>
+      </c>
+      <c r="AR80">
+        <v>0.31</v>
+      </c>
+      <c r="AS80">
+        <v>524</v>
+      </c>
+      <c r="AT80">
+        <v>536</v>
+      </c>
+      <c r="AU80">
+        <v>194</v>
+      </c>
+      <c r="AV80">
+        <v>258</v>
+      </c>
+      <c r="AW80">
+        <v>247</v>
+      </c>
+      <c r="AX80">
+        <v>199</v>
+      </c>
+      <c r="AY80">
+        <v>19</v>
+      </c>
+      <c r="AZ80">
+        <v>17</v>
+      </c>
+      <c r="BA80">
+        <v>5</v>
+      </c>
+      <c r="BB80">
+        <v>4</v>
+      </c>
+      <c r="BC80">
+        <v>16</v>
+      </c>
+      <c r="BD80">
+        <v>12</v>
+      </c>
+      <c r="BE80">
+        <v>34</v>
+      </c>
+      <c r="BF80">
+        <v>17</v>
+      </c>
+      <c r="BG80">
+        <v>2</v>
+      </c>
+      <c r="BH80">
+        <v>3</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK80">
+        <v>10</v>
+      </c>
+      <c r="BL80">
+        <v>9</v>
+      </c>
+      <c r="BM80">
+        <v>5</v>
+      </c>
+      <c r="BN80">
+        <v>8</v>
+      </c>
+      <c r="BO80">
+        <v>1</v>
+      </c>
+      <c r="BP80">
+        <v>4</v>
+      </c>
+      <c r="BQ80">
+        <v>22</v>
+      </c>
+      <c r="BR80">
+        <v>26</v>
+      </c>
+      <c r="BS80">
+        <v>2</v>
+      </c>
+      <c r="BT80">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW80">
+        <v>34</v>
+      </c>
+      <c r="BX80">
+        <v>42</v>
+      </c>
+      <c r="BY80">
+        <v>25</v>
+      </c>
+      <c r="BZ80">
+        <v>29</v>
+      </c>
+      <c r="CA80">
+        <v>9</v>
+      </c>
+      <c r="CB80">
+        <v>13</v>
+      </c>
+      <c r="CC80">
+        <v>10</v>
+      </c>
+      <c r="CD80">
+        <v>5</v>
+      </c>
+      <c r="CE80" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF80" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG80">
+        <v>3</v>
+      </c>
+      <c r="CH80">
+        <v>1</v>
+      </c>
+      <c r="CI80">
+        <v>0</v>
+      </c>
+      <c r="CJ80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:88" ht="30">
+      <c r="B81" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D81" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+      <c r="G81">
+        <v>60</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="I81">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J81">
+        <v>2.52</v>
+      </c>
+      <c r="K81">
+        <v>18</v>
+      </c>
+      <c r="L81">
+        <v>18</v>
+      </c>
+      <c r="M81">
+        <v>4</v>
+      </c>
+      <c r="N81">
+        <v>8</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>7</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>4</v>
+      </c>
+      <c r="S81">
+        <v>455</v>
+      </c>
+      <c r="T81">
+        <v>263</v>
+      </c>
+      <c r="U81">
+        <v>8</v>
+      </c>
+      <c r="V81">
+        <v>16</v>
+      </c>
+      <c r="W81">
+        <v>6</v>
+      </c>
+      <c r="X81">
+        <v>4</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA81">
+        <v>9</v>
+      </c>
+      <c r="AB81">
+        <v>6</v>
+      </c>
+      <c r="AC81">
+        <v>5</v>
+      </c>
+      <c r="AD81">
+        <v>4</v>
+      </c>
+      <c r="AE81">
+        <v>0</v>
+      </c>
+      <c r="AF81">
+        <v>0</v>
+      </c>
+      <c r="AG81">
+        <v>13</v>
+      </c>
+      <c r="AH81">
+        <v>12</v>
+      </c>
+      <c r="AI81">
+        <v>5</v>
+      </c>
+      <c r="AJ81">
+        <v>6</v>
+      </c>
+      <c r="AK81">
+        <v>0.79</v>
+      </c>
+      <c r="AL81">
+        <v>1.36</v>
+      </c>
+      <c r="AM81">
+        <v>0.33</v>
+      </c>
+      <c r="AN81">
+        <v>0.37</v>
+      </c>
+      <c r="AO81">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AP81">
+        <v>1.73</v>
+      </c>
+      <c r="AQ81">
+        <v>0.76</v>
+      </c>
+      <c r="AR81">
+        <v>3.44</v>
+      </c>
+      <c r="AS81">
+        <v>541</v>
+      </c>
+      <c r="AT81">
+        <v>342</v>
+      </c>
+      <c r="AU81">
+        <v>256</v>
+      </c>
+      <c r="AV81">
+        <v>120</v>
+      </c>
+      <c r="AW81">
+        <v>199</v>
+      </c>
+      <c r="AX81">
+        <v>143</v>
+      </c>
+      <c r="AY81">
+        <v>16</v>
+      </c>
+      <c r="AZ81">
+        <v>13</v>
+      </c>
+      <c r="BA81">
+        <v>3</v>
+      </c>
+      <c r="BB81">
+        <v>5</v>
+      </c>
+      <c r="BC81">
+        <v>19</v>
+      </c>
+      <c r="BD81">
+        <v>14</v>
+      </c>
+      <c r="BE81">
+        <v>32</v>
+      </c>
+      <c r="BF81">
+        <v>32</v>
+      </c>
+      <c r="BG81">
+        <v>1</v>
+      </c>
+      <c r="BH81">
+        <v>2</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK81">
+        <v>9</v>
+      </c>
+      <c r="BL81">
+        <v>16</v>
+      </c>
+      <c r="BM81">
+        <v>9</v>
+      </c>
+      <c r="BN81">
+        <v>10</v>
+      </c>
+      <c r="BO81">
+        <v>4</v>
+      </c>
+      <c r="BP81">
+        <v>6</v>
+      </c>
+      <c r="BQ81">
+        <v>22</v>
+      </c>
+      <c r="BR81">
+        <v>24</v>
+      </c>
+      <c r="BS81">
+        <v>4</v>
+      </c>
+      <c r="BT81">
+        <v>2</v>
+      </c>
+      <c r="BU81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW81">
+        <v>43</v>
+      </c>
+      <c r="BX81">
+        <v>47</v>
+      </c>
+      <c r="BY81">
+        <v>36</v>
+      </c>
+      <c r="BZ81">
+        <v>34</v>
+      </c>
+      <c r="CA81">
+        <v>7</v>
+      </c>
+      <c r="CB81">
+        <v>13</v>
+      </c>
+      <c r="CC81">
+        <v>12</v>
+      </c>
+      <c r="CD81">
+        <v>11</v>
+      </c>
+      <c r="CE81" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF81" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG81">
+        <v>2</v>
+      </c>
+      <c r="CH81">
+        <v>3</v>
+      </c>
+      <c r="CI81">
+        <v>0</v>
+      </c>
+      <c r="CJ81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:88">
+      <c r="B82" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C82" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>58</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I82">
+        <v>2.94</v>
+      </c>
+      <c r="J82">
+        <v>1.07</v>
+      </c>
+      <c r="K82">
+        <v>16</v>
+      </c>
+      <c r="L82">
+        <v>16</v>
+      </c>
+      <c r="M82">
+        <v>6</v>
+      </c>
+      <c r="N82">
+        <v>6</v>
+      </c>
+      <c r="O82">
+        <v>3</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>356</v>
+      </c>
+      <c r="T82">
+        <v>246</v>
+      </c>
+      <c r="U82">
+        <v>14</v>
+      </c>
+      <c r="V82">
+        <v>14</v>
+      </c>
+      <c r="W82">
+        <v>5</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA82">
+        <v>4</v>
+      </c>
+      <c r="AB82">
+        <v>9</v>
+      </c>
+      <c r="AC82">
+        <v>6</v>
+      </c>
+      <c r="AD82">
+        <v>1</v>
+      </c>
+      <c r="AE82">
+        <v>2</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>8</v>
+      </c>
+      <c r="AH82">
+        <v>11</v>
+      </c>
+      <c r="AI82">
+        <v>8</v>
+      </c>
+      <c r="AJ82">
+        <v>5</v>
+      </c>
+      <c r="AK82">
+        <v>1.04</v>
+      </c>
+      <c r="AL82">
+        <v>0.46</v>
+      </c>
+      <c r="AM82">
+        <v>0.32</v>
+      </c>
+      <c r="AN82">
+        <v>0.61</v>
+      </c>
+      <c r="AO82">
+        <v>1.36</v>
+      </c>
+      <c r="AP82">
+        <v>1.07</v>
+      </c>
+      <c r="AQ82">
+        <v>2.82</v>
+      </c>
+      <c r="AR82">
+        <v>1.55</v>
+      </c>
+      <c r="AS82">
+        <v>433</v>
+      </c>
+      <c r="AT82">
+        <v>318</v>
+      </c>
+      <c r="AU82">
+        <v>171</v>
+      </c>
+      <c r="AV82">
+        <v>133</v>
+      </c>
+      <c r="AW82">
+        <v>185</v>
+      </c>
+      <c r="AX82">
+        <v>113</v>
+      </c>
+      <c r="AY82">
+        <v>10</v>
+      </c>
+      <c r="AZ82">
+        <v>31</v>
+      </c>
+      <c r="BA82">
+        <v>6</v>
+      </c>
+      <c r="BB82">
+        <v>6</v>
+      </c>
+      <c r="BC82">
+        <v>20</v>
+      </c>
+      <c r="BD82">
+        <v>18</v>
+      </c>
+      <c r="BE82">
+        <v>22</v>
+      </c>
+      <c r="BF82">
+        <v>30</v>
+      </c>
+      <c r="BG82">
+        <v>1</v>
+      </c>
+      <c r="BH82">
+        <v>0</v>
+      </c>
+      <c r="BI82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK82">
+        <v>12</v>
+      </c>
+      <c r="BL82">
+        <v>18</v>
+      </c>
+      <c r="BM82">
+        <v>8</v>
+      </c>
+      <c r="BN82">
+        <v>6</v>
+      </c>
+      <c r="BO82">
+        <v>1</v>
+      </c>
+      <c r="BP82">
+        <v>4</v>
+      </c>
+      <c r="BQ82">
+        <v>20</v>
+      </c>
+      <c r="BR82">
+        <v>32</v>
+      </c>
+      <c r="BS82">
+        <v>5</v>
+      </c>
+      <c r="BT82">
+        <v>3</v>
+      </c>
+      <c r="BU82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW82">
+        <v>56</v>
+      </c>
+      <c r="BX82">
+        <v>54</v>
+      </c>
+      <c r="BY82">
+        <v>35</v>
+      </c>
+      <c r="BZ82">
+        <v>33</v>
+      </c>
+      <c r="CA82">
+        <v>21</v>
+      </c>
+      <c r="CB82">
+        <v>21</v>
+      </c>
+      <c r="CC82">
+        <v>12</v>
+      </c>
+      <c r="CD82">
+        <v>2</v>
+      </c>
+      <c r="CE82" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF82" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG82">
+        <v>2</v>
+      </c>
+      <c r="CH82">
+        <v>3</v>
+      </c>
+      <c r="CI82">
+        <v>0</v>
+      </c>
+      <c r="CJ82">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3D35629-E86E-4495-9CD0-347BC84A87DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB14C2E0-7A91-464C-BEC3-F5F165618004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="188">
   <si>
     <t>date</t>
   </si>
@@ -598,6 +598,12 @@
   <si>
     <t>Sat 10 October, 14:45</t>
   </si>
+  <si>
+    <t>Sat 10 October, 17:30</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 20:15</t>
+  </si>
 </sst>
 </file>
 
@@ -1008,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ82"/>
+  <dimension ref="A1:CJ84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1343,7 +1349,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H82" si="0">100-G2</f>
+        <f t="shared" ref="H2:H84" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -5592,7 +5598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:88" ht="25.5">
+    <row r="18" spans="1:88">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6927,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:88" ht="25.5">
+    <row r="23" spans="1:88">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7194,7 +7200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:88" ht="25.5">
+    <row r="24" spans="1:88">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7995,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:88" ht="25.5">
+    <row r="27" spans="1:88">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8529,7 +8535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:88" ht="25.5">
+    <row r="29" spans="1:88">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:88" ht="25.5">
+    <row r="30" spans="1:88">
       <c r="A30">
         <v>29</v>
       </c>
@@ -10929,7 +10935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:88" ht="25.5">
+    <row r="38" spans="1:88">
       <c r="B38" s="4" t="s">
         <v>142</v>
       </c>
@@ -11193,7 +11199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:88" ht="25.5">
+    <row r="39" spans="1:88">
       <c r="B39" s="4" t="s">
         <v>143</v>
       </c>
@@ -12249,7 +12255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:88" ht="25.5">
+    <row r="43" spans="1:88">
       <c r="B43" s="2" t="s">
         <v>147</v>
       </c>
@@ -12777,7 +12783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:88" ht="25.5">
+    <row r="45" spans="1:88">
       <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
@@ -13305,7 +13311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:88" ht="25.5">
+    <row r="47" spans="1:88">
       <c r="B47" s="4" t="s">
         <v>151</v>
       </c>
@@ -13569,7 +13575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:88" ht="25.5">
+    <row r="48" spans="1:88">
       <c r="B48" s="4" t="s">
         <v>152</v>
       </c>
@@ -22806,6 +22812,534 @@
         <v>0</v>
       </c>
       <c r="CJ82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:88">
+      <c r="B83" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>4</v>
+      </c>
+      <c r="G83">
+        <v>40</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I83">
+        <v>0.77</v>
+      </c>
+      <c r="J83">
+        <v>2.04</v>
+      </c>
+      <c r="K83">
+        <v>7</v>
+      </c>
+      <c r="L83">
+        <v>16</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>5</v>
+      </c>
+      <c r="O83">
+        <v>2</v>
+      </c>
+      <c r="P83">
+        <v>4</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+      <c r="R83">
+        <v>2</v>
+      </c>
+      <c r="S83">
+        <v>251</v>
+      </c>
+      <c r="T83">
+        <v>444</v>
+      </c>
+      <c r="U83">
+        <v>13</v>
+      </c>
+      <c r="V83">
+        <v>11</v>
+      </c>
+      <c r="W83">
+        <v>3</v>
+      </c>
+      <c r="X83">
+        <v>4</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA83">
+        <v>3</v>
+      </c>
+      <c r="AB83">
+        <v>5</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83">
+        <v>6</v>
+      </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>5</v>
+      </c>
+      <c r="AH83">
+        <v>12</v>
+      </c>
+      <c r="AI83">
+        <v>2</v>
+      </c>
+      <c r="AJ83">
+        <v>4</v>
+      </c>
+      <c r="AK83">
+        <v>0.63</v>
+      </c>
+      <c r="AL83">
+        <v>1.79</v>
+      </c>
+      <c r="AM83">
+        <v>0.13</v>
+      </c>
+      <c r="AN83">
+        <v>0.25</v>
+      </c>
+      <c r="AO83">
+        <v>0.77</v>
+      </c>
+      <c r="AP83">
+        <v>2.04</v>
+      </c>
+      <c r="AQ83">
+        <v>0.41</v>
+      </c>
+      <c r="AR83">
+        <v>2.6</v>
+      </c>
+      <c r="AS83">
+        <v>341</v>
+      </c>
+      <c r="AT83">
+        <v>517</v>
+      </c>
+      <c r="AU83">
+        <v>114</v>
+      </c>
+      <c r="AV83">
+        <v>225</v>
+      </c>
+      <c r="AW83">
+        <v>137</v>
+      </c>
+      <c r="AX83">
+        <v>219</v>
+      </c>
+      <c r="AY83">
+        <v>15</v>
+      </c>
+      <c r="AZ83">
+        <v>23</v>
+      </c>
+      <c r="BA83">
+        <v>3</v>
+      </c>
+      <c r="BB83">
+        <v>4</v>
+      </c>
+      <c r="BC83">
+        <v>15</v>
+      </c>
+      <c r="BD83">
+        <v>22</v>
+      </c>
+      <c r="BE83">
+        <v>22</v>
+      </c>
+      <c r="BF83">
+        <v>27</v>
+      </c>
+      <c r="BG83">
+        <v>2</v>
+      </c>
+      <c r="BH83">
+        <v>3</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK83">
+        <v>16</v>
+      </c>
+      <c r="BL83">
+        <v>8</v>
+      </c>
+      <c r="BM83">
+        <v>10</v>
+      </c>
+      <c r="BN83">
+        <v>9</v>
+      </c>
+      <c r="BO83">
+        <v>6</v>
+      </c>
+      <c r="BP83">
+        <v>1</v>
+      </c>
+      <c r="BQ83">
+        <v>19</v>
+      </c>
+      <c r="BR83">
+        <v>30</v>
+      </c>
+      <c r="BS83">
+        <v>1</v>
+      </c>
+      <c r="BT83">
+        <v>2</v>
+      </c>
+      <c r="BU83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW83">
+        <v>41</v>
+      </c>
+      <c r="BX83">
+        <v>37</v>
+      </c>
+      <c r="BY83">
+        <v>31</v>
+      </c>
+      <c r="BZ83">
+        <v>24</v>
+      </c>
+      <c r="CA83">
+        <v>10</v>
+      </c>
+      <c r="CB83">
+        <v>13</v>
+      </c>
+      <c r="CC83">
+        <v>5</v>
+      </c>
+      <c r="CD83">
+        <v>4</v>
+      </c>
+      <c r="CE83" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF83" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG83">
+        <v>2</v>
+      </c>
+      <c r="CH83">
+        <v>4</v>
+      </c>
+      <c r="CI83">
+        <v>0</v>
+      </c>
+      <c r="CJ83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:88" ht="30">
+      <c r="B84" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84">
+        <v>57</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I84">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J84">
+        <v>2.12</v>
+      </c>
+      <c r="K84">
+        <v>11</v>
+      </c>
+      <c r="L84">
+        <v>15</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84">
+        <v>9</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>4</v>
+      </c>
+      <c r="Q84">
+        <v>1</v>
+      </c>
+      <c r="R84">
+        <v>1</v>
+      </c>
+      <c r="S84">
+        <v>400</v>
+      </c>
+      <c r="T84">
+        <v>289</v>
+      </c>
+      <c r="U84">
+        <v>13</v>
+      </c>
+      <c r="V84">
+        <v>18</v>
+      </c>
+      <c r="W84">
+        <v>4</v>
+      </c>
+      <c r="X84">
+        <v>4</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA84">
+        <v>5</v>
+      </c>
+      <c r="AB84">
+        <v>2</v>
+      </c>
+      <c r="AC84">
+        <v>3</v>
+      </c>
+      <c r="AD84">
+        <v>4</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>6</v>
+      </c>
+      <c r="AH84">
+        <v>14</v>
+      </c>
+      <c r="AI84">
+        <v>5</v>
+      </c>
+      <c r="AJ84">
+        <v>1</v>
+      </c>
+      <c r="AK84">
+        <v>0.52</v>
+      </c>
+      <c r="AL84">
+        <v>1.73</v>
+      </c>
+      <c r="AM84">
+        <v>0.05</v>
+      </c>
+      <c r="AN84">
+        <v>0.39</v>
+      </c>
+      <c r="AO84">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AP84">
+        <v>2.12</v>
+      </c>
+      <c r="AQ84">
+        <v>0.96</v>
+      </c>
+      <c r="AR84">
+        <v>3.12</v>
+      </c>
+      <c r="AS84">
+        <v>496</v>
+      </c>
+      <c r="AT84">
+        <v>371</v>
+      </c>
+      <c r="AU84">
+        <v>234</v>
+      </c>
+      <c r="AV84">
+        <v>138</v>
+      </c>
+      <c r="AW84">
+        <v>166</v>
+      </c>
+      <c r="AX84">
+        <v>151</v>
+      </c>
+      <c r="AY84">
+        <v>30</v>
+      </c>
+      <c r="AZ84">
+        <v>27</v>
+      </c>
+      <c r="BA84">
+        <v>2</v>
+      </c>
+      <c r="BB84">
+        <v>4</v>
+      </c>
+      <c r="BC84">
+        <v>22</v>
+      </c>
+      <c r="BD84">
+        <v>15</v>
+      </c>
+      <c r="BE84">
+        <v>20</v>
+      </c>
+      <c r="BF84">
+        <v>30</v>
+      </c>
+      <c r="BG84">
+        <v>2</v>
+      </c>
+      <c r="BH84">
+        <v>0</v>
+      </c>
+      <c r="BI84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK84">
+        <v>19</v>
+      </c>
+      <c r="BL84">
+        <v>11</v>
+      </c>
+      <c r="BM84">
+        <v>9</v>
+      </c>
+      <c r="BN84">
+        <v>10</v>
+      </c>
+      <c r="BO84">
+        <v>3</v>
+      </c>
+      <c r="BP84">
+        <v>3</v>
+      </c>
+      <c r="BQ84">
+        <v>27</v>
+      </c>
+      <c r="BR84">
+        <v>22</v>
+      </c>
+      <c r="BS84">
+        <v>6</v>
+      </c>
+      <c r="BT84">
+        <v>3</v>
+      </c>
+      <c r="BU84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW84">
+        <v>57</v>
+      </c>
+      <c r="BX84">
+        <v>48</v>
+      </c>
+      <c r="BY84">
+        <v>42</v>
+      </c>
+      <c r="BZ84">
+        <v>34</v>
+      </c>
+      <c r="CA84">
+        <v>15</v>
+      </c>
+      <c r="CB84">
+        <v>14</v>
+      </c>
+      <c r="CC84">
+        <v>5</v>
+      </c>
+      <c r="CD84">
+        <v>10</v>
+      </c>
+      <c r="CE84" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF84" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG84">
+        <v>2</v>
+      </c>
+      <c r="CH84">
+        <v>4</v>
+      </c>
+      <c r="CI84">
+        <v>0</v>
+      </c>
+      <c r="CJ84">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB14C2E0-7A91-464C-BEC3-F5F165618004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13C4D69C-E7CE-4BCB-B506-7354E671E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="193">
   <si>
     <t>date</t>
   </si>
@@ -604,6 +604,21 @@
   <si>
     <t>Sat 10 October, 20:15</t>
   </si>
+  <si>
+    <t>Sun 11 October, 14:45</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 17:30</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 20:15</t>
+  </si>
+  <si>
+    <t>Mon 12 October, 18:00</t>
+  </si>
+  <si>
+    <t>Mon 12 October, 20:30</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ84"/>
+  <dimension ref="A1:CJ89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1349,7 +1364,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H84" si="0">100-G2</f>
+        <f t="shared" ref="H2:H89" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -23340,6 +23355,1326 @@
         <v>0</v>
       </c>
       <c r="CJ84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:88">
+      <c r="B85" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>54</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I85">
+        <v>1.64</v>
+      </c>
+      <c r="J85">
+        <v>1.76</v>
+      </c>
+      <c r="K85">
+        <v>18</v>
+      </c>
+      <c r="L85">
+        <v>17</v>
+      </c>
+      <c r="M85">
+        <v>5</v>
+      </c>
+      <c r="N85">
+        <v>3</v>
+      </c>
+      <c r="O85">
+        <v>3</v>
+      </c>
+      <c r="P85">
+        <v>5</v>
+      </c>
+      <c r="Q85">
+        <v>2</v>
+      </c>
+      <c r="R85">
+        <v>4</v>
+      </c>
+      <c r="S85">
+        <v>356</v>
+      </c>
+      <c r="T85">
+        <v>270</v>
+      </c>
+      <c r="U85">
+        <v>12</v>
+      </c>
+      <c r="V85">
+        <v>16</v>
+      </c>
+      <c r="W85">
+        <v>6</v>
+      </c>
+      <c r="X85">
+        <v>13</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA85">
+        <v>6</v>
+      </c>
+      <c r="AB85">
+        <v>7</v>
+      </c>
+      <c r="AC85">
+        <v>7</v>
+      </c>
+      <c r="AD85">
+        <v>7</v>
+      </c>
+      <c r="AE85">
+        <v>1</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>10</v>
+      </c>
+      <c r="AH85">
+        <v>11</v>
+      </c>
+      <c r="AI85">
+        <v>8</v>
+      </c>
+      <c r="AJ85">
+        <v>6</v>
+      </c>
+      <c r="AK85">
+        <v>1.49</v>
+      </c>
+      <c r="AL85">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AM85">
+        <v>0.15</v>
+      </c>
+      <c r="AN85">
+        <v>0.62</v>
+      </c>
+      <c r="AO85">
+        <v>1.64</v>
+      </c>
+      <c r="AP85">
+        <v>1.76</v>
+      </c>
+      <c r="AQ85">
+        <v>1.25</v>
+      </c>
+      <c r="AR85">
+        <v>0.4</v>
+      </c>
+      <c r="AS85">
+        <v>422</v>
+      </c>
+      <c r="AT85">
+        <v>334</v>
+      </c>
+      <c r="AU85">
+        <v>154</v>
+      </c>
+      <c r="AV85">
+        <v>126</v>
+      </c>
+      <c r="AW85">
+        <v>202</v>
+      </c>
+      <c r="AX85">
+        <v>144</v>
+      </c>
+      <c r="AY85">
+        <v>20</v>
+      </c>
+      <c r="AZ85">
+        <v>12</v>
+      </c>
+      <c r="BA85">
+        <v>5</v>
+      </c>
+      <c r="BB85">
+        <v>8</v>
+      </c>
+      <c r="BC85">
+        <v>11</v>
+      </c>
+      <c r="BD85">
+        <v>13</v>
+      </c>
+      <c r="BE85">
+        <v>22</v>
+      </c>
+      <c r="BF85">
+        <v>47</v>
+      </c>
+      <c r="BG85">
+        <v>2</v>
+      </c>
+      <c r="BH85">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK85">
+        <v>14</v>
+      </c>
+      <c r="BL85">
+        <v>14</v>
+      </c>
+      <c r="BM85">
+        <v>6</v>
+      </c>
+      <c r="BN85">
+        <v>2</v>
+      </c>
+      <c r="BO85">
+        <v>6</v>
+      </c>
+      <c r="BP85">
+        <v>7</v>
+      </c>
+      <c r="BQ85">
+        <v>42</v>
+      </c>
+      <c r="BR85">
+        <v>26</v>
+      </c>
+      <c r="BS85">
+        <v>2</v>
+      </c>
+      <c r="BT85">
+        <v>4</v>
+      </c>
+      <c r="BU85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW85">
+        <v>48</v>
+      </c>
+      <c r="BX85">
+        <v>45</v>
+      </c>
+      <c r="BY85">
+        <v>38</v>
+      </c>
+      <c r="BZ85">
+        <v>32</v>
+      </c>
+      <c r="CA85">
+        <v>10</v>
+      </c>
+      <c r="CB85">
+        <v>13</v>
+      </c>
+      <c r="CC85">
+        <v>8</v>
+      </c>
+      <c r="CD85">
+        <v>6</v>
+      </c>
+      <c r="CE85" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF85" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG85">
+        <v>2</v>
+      </c>
+      <c r="CH85">
+        <v>2</v>
+      </c>
+      <c r="CI85">
+        <v>0</v>
+      </c>
+      <c r="CJ85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:88">
+      <c r="B86" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" t="s">
+        <v>96</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>48</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="I86">
+        <v>0.87</v>
+      </c>
+      <c r="J86">
+        <v>0.8</v>
+      </c>
+      <c r="K86">
+        <v>7</v>
+      </c>
+      <c r="L86">
+        <v>17</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>3</v>
+      </c>
+      <c r="O86">
+        <v>2</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>339</v>
+      </c>
+      <c r="T86">
+        <v>356</v>
+      </c>
+      <c r="U86">
+        <v>21</v>
+      </c>
+      <c r="V86">
+        <v>6</v>
+      </c>
+      <c r="W86">
+        <v>2</v>
+      </c>
+      <c r="X86">
+        <v>7</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA86">
+        <v>4</v>
+      </c>
+      <c r="AB86">
+        <v>8</v>
+      </c>
+      <c r="AC86">
+        <v>1</v>
+      </c>
+      <c r="AD86">
+        <v>6</v>
+      </c>
+      <c r="AE86">
+        <v>1</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>5</v>
+      </c>
+      <c r="AH86">
+        <v>12</v>
+      </c>
+      <c r="AI86">
+        <v>2</v>
+      </c>
+      <c r="AJ86">
+        <v>5</v>
+      </c>
+      <c r="AK86">
+        <v>0.87</v>
+      </c>
+      <c r="AL86">
+        <v>0.64</v>
+      </c>
+      <c r="AM86">
+        <v>0</v>
+      </c>
+      <c r="AN86">
+        <v>0.15</v>
+      </c>
+      <c r="AO86">
+        <v>0.87</v>
+      </c>
+      <c r="AP86">
+        <v>0.8</v>
+      </c>
+      <c r="AQ86">
+        <v>1.48</v>
+      </c>
+      <c r="AR86">
+        <v>0.94</v>
+      </c>
+      <c r="AS86">
+        <v>403</v>
+      </c>
+      <c r="AT86">
+        <v>414</v>
+      </c>
+      <c r="AU86">
+        <v>180</v>
+      </c>
+      <c r="AV86">
+        <v>181</v>
+      </c>
+      <c r="AW86">
+        <v>159</v>
+      </c>
+      <c r="AX86">
+        <v>175</v>
+      </c>
+      <c r="AY86">
+        <v>19</v>
+      </c>
+      <c r="AZ86">
+        <v>25</v>
+      </c>
+      <c r="BA86">
+        <v>4</v>
+      </c>
+      <c r="BB86">
+        <v>6</v>
+      </c>
+      <c r="BC86">
+        <v>9</v>
+      </c>
+      <c r="BD86">
+        <v>20</v>
+      </c>
+      <c r="BE86">
+        <v>22</v>
+      </c>
+      <c r="BF86">
+        <v>23</v>
+      </c>
+      <c r="BG86">
+        <v>0</v>
+      </c>
+      <c r="BH86">
+        <v>2</v>
+      </c>
+      <c r="BI86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK86">
+        <v>9</v>
+      </c>
+      <c r="BL86">
+        <v>11</v>
+      </c>
+      <c r="BM86">
+        <v>7</v>
+      </c>
+      <c r="BN86">
+        <v>9</v>
+      </c>
+      <c r="BO86">
+        <v>6</v>
+      </c>
+      <c r="BP86">
+        <v>1</v>
+      </c>
+      <c r="BQ86">
+        <v>27</v>
+      </c>
+      <c r="BR86">
+        <v>18</v>
+      </c>
+      <c r="BS86">
+        <v>3</v>
+      </c>
+      <c r="BT86">
+        <v>0</v>
+      </c>
+      <c r="BU86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW86">
+        <v>42</v>
+      </c>
+      <c r="BX86">
+        <v>56</v>
+      </c>
+      <c r="BY86">
+        <v>28</v>
+      </c>
+      <c r="BZ86">
+        <v>44</v>
+      </c>
+      <c r="CA86">
+        <v>14</v>
+      </c>
+      <c r="CB86">
+        <v>12</v>
+      </c>
+      <c r="CC86">
+        <v>13</v>
+      </c>
+      <c r="CD86">
+        <v>12</v>
+      </c>
+      <c r="CE86" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF86" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG86">
+        <v>2</v>
+      </c>
+      <c r="CH86">
+        <v>0</v>
+      </c>
+      <c r="CI86">
+        <v>0</v>
+      </c>
+      <c r="CJ86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:88" ht="30">
+      <c r="B87" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>49</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="I87">
+        <v>1.32</v>
+      </c>
+      <c r="J87">
+        <v>0.83</v>
+      </c>
+      <c r="K87">
+        <v>15</v>
+      </c>
+      <c r="L87">
+        <v>15</v>
+      </c>
+      <c r="M87">
+        <v>8</v>
+      </c>
+      <c r="N87">
+        <v>7</v>
+      </c>
+      <c r="O87">
+        <v>2</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>370</v>
+      </c>
+      <c r="T87">
+        <v>389</v>
+      </c>
+      <c r="U87">
+        <v>17</v>
+      </c>
+      <c r="V87">
+        <v>15</v>
+      </c>
+      <c r="W87">
+        <v>5</v>
+      </c>
+      <c r="X87">
+        <v>3</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA87">
+        <v>2</v>
+      </c>
+      <c r="AB87">
+        <v>6</v>
+      </c>
+      <c r="AC87">
+        <v>5</v>
+      </c>
+      <c r="AD87">
+        <v>2</v>
+      </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>0</v>
+      </c>
+      <c r="AG87">
+        <v>10</v>
+      </c>
+      <c r="AH87">
+        <v>9</v>
+      </c>
+      <c r="AI87">
+        <v>5</v>
+      </c>
+      <c r="AJ87">
+        <v>6</v>
+      </c>
+      <c r="AK87">
+        <v>0.89</v>
+      </c>
+      <c r="AL87">
+        <v>0.69</v>
+      </c>
+      <c r="AM87">
+        <v>0.43</v>
+      </c>
+      <c r="AN87">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AO87">
+        <v>1.32</v>
+      </c>
+      <c r="AP87">
+        <v>0.83</v>
+      </c>
+      <c r="AQ87">
+        <v>1.97</v>
+      </c>
+      <c r="AR87">
+        <v>0.76</v>
+      </c>
+      <c r="AS87">
+        <v>443</v>
+      </c>
+      <c r="AT87">
+        <v>467</v>
+      </c>
+      <c r="AU87">
+        <v>220</v>
+      </c>
+      <c r="AV87">
+        <v>178</v>
+      </c>
+      <c r="AW87">
+        <v>150</v>
+      </c>
+      <c r="AX87">
+        <v>211</v>
+      </c>
+      <c r="AY87">
+        <v>15</v>
+      </c>
+      <c r="AZ87">
+        <v>21</v>
+      </c>
+      <c r="BA87">
+        <v>4</v>
+      </c>
+      <c r="BB87">
+        <v>4</v>
+      </c>
+      <c r="BC87">
+        <v>18</v>
+      </c>
+      <c r="BD87">
+        <v>11</v>
+      </c>
+      <c r="BE87">
+        <v>28</v>
+      </c>
+      <c r="BF87">
+        <v>23</v>
+      </c>
+      <c r="BG87">
+        <v>1</v>
+      </c>
+      <c r="BH87">
+        <v>0</v>
+      </c>
+      <c r="BI87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK87">
+        <v>16</v>
+      </c>
+      <c r="BL87">
+        <v>24</v>
+      </c>
+      <c r="BM87">
+        <v>12</v>
+      </c>
+      <c r="BN87">
+        <v>10</v>
+      </c>
+      <c r="BO87">
+        <v>2</v>
+      </c>
+      <c r="BP87">
+        <v>5</v>
+      </c>
+      <c r="BQ87">
+        <v>19</v>
+      </c>
+      <c r="BR87">
+        <v>17</v>
+      </c>
+      <c r="BS87">
+        <v>7</v>
+      </c>
+      <c r="BT87">
+        <v>6</v>
+      </c>
+      <c r="BU87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW87">
+        <v>58</v>
+      </c>
+      <c r="BX87">
+        <v>58</v>
+      </c>
+      <c r="BY87">
+        <v>44</v>
+      </c>
+      <c r="BZ87">
+        <v>49</v>
+      </c>
+      <c r="CA87">
+        <v>14</v>
+      </c>
+      <c r="CB87">
+        <v>9</v>
+      </c>
+      <c r="CC87">
+        <v>14</v>
+      </c>
+      <c r="CD87">
+        <v>8</v>
+      </c>
+      <c r="CE87" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF87" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG87">
+        <v>1</v>
+      </c>
+      <c r="CH87">
+        <v>4</v>
+      </c>
+      <c r="CI87">
+        <v>0</v>
+      </c>
+      <c r="CJ87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:88" ht="30">
+      <c r="B88" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D88" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88">
+        <v>45</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="I88">
+        <v>0.86</v>
+      </c>
+      <c r="J88">
+        <v>2.58</v>
+      </c>
+      <c r="K88">
+        <v>6</v>
+      </c>
+      <c r="L88">
+        <v>22</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>11</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>4</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
+        <v>290</v>
+      </c>
+      <c r="T88">
+        <v>370</v>
+      </c>
+      <c r="U88">
+        <v>14</v>
+      </c>
+      <c r="V88">
+        <v>16</v>
+      </c>
+      <c r="W88">
+        <v>3</v>
+      </c>
+      <c r="X88">
+        <v>5</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA88">
+        <v>1</v>
+      </c>
+      <c r="AB88">
+        <v>7</v>
+      </c>
+      <c r="AC88">
+        <v>3</v>
+      </c>
+      <c r="AD88">
+        <v>4</v>
+      </c>
+      <c r="AE88">
+        <v>0</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>4</v>
+      </c>
+      <c r="AH88">
+        <v>15</v>
+      </c>
+      <c r="AI88">
+        <v>2</v>
+      </c>
+      <c r="AJ88">
+        <v>7</v>
+      </c>
+      <c r="AK88">
+        <v>0.1</v>
+      </c>
+      <c r="AL88">
+        <v>0.97</v>
+      </c>
+      <c r="AM88">
+        <v>0.76</v>
+      </c>
+      <c r="AN88">
+        <v>0.82</v>
+      </c>
+      <c r="AO88">
+        <v>0.86</v>
+      </c>
+      <c r="AP88">
+        <v>1.79</v>
+      </c>
+      <c r="AQ88">
+        <v>1.43</v>
+      </c>
+      <c r="AR88">
+        <v>3.81</v>
+      </c>
+      <c r="AS88">
+        <v>362</v>
+      </c>
+      <c r="AT88">
+        <v>426</v>
+      </c>
+      <c r="AU88">
+        <v>182</v>
+      </c>
+      <c r="AV88">
+        <v>153</v>
+      </c>
+      <c r="AW88">
+        <v>108</v>
+      </c>
+      <c r="AX88">
+        <v>217</v>
+      </c>
+      <c r="AY88">
+        <v>18</v>
+      </c>
+      <c r="AZ88">
+        <v>24</v>
+      </c>
+      <c r="BA88">
+        <v>4</v>
+      </c>
+      <c r="BB88">
+        <v>5</v>
+      </c>
+      <c r="BC88">
+        <v>14</v>
+      </c>
+      <c r="BD88">
+        <v>17</v>
+      </c>
+      <c r="BE88">
+        <v>12</v>
+      </c>
+      <c r="BF88">
+        <v>41</v>
+      </c>
+      <c r="BG88">
+        <v>0</v>
+      </c>
+      <c r="BH88">
+        <v>5</v>
+      </c>
+      <c r="BI88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK88">
+        <v>14</v>
+      </c>
+      <c r="BL88">
+        <v>19</v>
+      </c>
+      <c r="BM88">
+        <v>10</v>
+      </c>
+      <c r="BN88">
+        <v>10</v>
+      </c>
+      <c r="BO88">
+        <v>5</v>
+      </c>
+      <c r="BP88">
+        <v>3</v>
+      </c>
+      <c r="BQ88">
+        <v>34</v>
+      </c>
+      <c r="BR88">
+        <v>22</v>
+      </c>
+      <c r="BS88">
+        <v>7</v>
+      </c>
+      <c r="BT88">
+        <v>0</v>
+      </c>
+      <c r="BU88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW88">
+        <v>56</v>
+      </c>
+      <c r="BX88">
+        <v>56</v>
+      </c>
+      <c r="BY88">
+        <v>43</v>
+      </c>
+      <c r="BZ88">
+        <v>39</v>
+      </c>
+      <c r="CA88">
+        <v>13</v>
+      </c>
+      <c r="CB88">
+        <v>17</v>
+      </c>
+      <c r="CC88">
+        <v>15</v>
+      </c>
+      <c r="CD88">
+        <v>7</v>
+      </c>
+      <c r="CE88" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF88" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG88">
+        <v>2</v>
+      </c>
+      <c r="CH88">
+        <v>5</v>
+      </c>
+      <c r="CI88">
+        <v>0</v>
+      </c>
+      <c r="CJ88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:88" ht="30">
+      <c r="B89" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>38</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="I89">
+        <v>0.87</v>
+      </c>
+      <c r="J89">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="K89">
+        <v>10</v>
+      </c>
+      <c r="L89">
+        <v>18</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89">
+        <v>4</v>
+      </c>
+      <c r="O89">
+        <v>2</v>
+      </c>
+      <c r="P89">
+        <v>3</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
+      </c>
+      <c r="S89">
+        <v>284</v>
+      </c>
+      <c r="T89">
+        <v>504</v>
+      </c>
+      <c r="U89">
+        <v>11</v>
+      </c>
+      <c r="V89">
+        <v>9</v>
+      </c>
+      <c r="W89">
+        <v>1</v>
+      </c>
+      <c r="X89">
+        <v>8</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA89">
+        <v>7</v>
+      </c>
+      <c r="AB89">
+        <v>9</v>
+      </c>
+      <c r="AC89">
+        <v>1</v>
+      </c>
+      <c r="AD89">
+        <v>5</v>
+      </c>
+      <c r="AE89">
+        <v>0</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>8</v>
+      </c>
+      <c r="AH89">
+        <v>13</v>
+      </c>
+      <c r="AI89">
+        <v>2</v>
+      </c>
+      <c r="AJ89">
+        <v>5</v>
+      </c>
+      <c r="AK89">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AL89">
+        <v>1.84</v>
+      </c>
+      <c r="AM89">
+        <v>0.3</v>
+      </c>
+      <c r="AN89">
+        <v>0.71</v>
+      </c>
+      <c r="AO89">
+        <v>0.87</v>
+      </c>
+      <c r="AP89">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AQ89">
+        <v>1.49</v>
+      </c>
+      <c r="AR89">
+        <v>1.43</v>
+      </c>
+      <c r="AS89">
+        <v>369</v>
+      </c>
+      <c r="AT89">
+        <v>606</v>
+      </c>
+      <c r="AU89">
+        <v>136</v>
+      </c>
+      <c r="AV89">
+        <v>250</v>
+      </c>
+      <c r="AW89">
+        <v>148</v>
+      </c>
+      <c r="AX89">
+        <v>254</v>
+      </c>
+      <c r="AY89">
+        <v>16</v>
+      </c>
+      <c r="AZ89">
+        <v>35</v>
+      </c>
+      <c r="BA89">
+        <v>3</v>
+      </c>
+      <c r="BB89">
+        <v>6</v>
+      </c>
+      <c r="BC89">
+        <v>22</v>
+      </c>
+      <c r="BD89">
+        <v>23</v>
+      </c>
+      <c r="BE89">
+        <v>17</v>
+      </c>
+      <c r="BF89">
+        <v>28</v>
+      </c>
+      <c r="BG89">
+        <v>3</v>
+      </c>
+      <c r="BH89">
+        <v>2</v>
+      </c>
+      <c r="BI89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK89">
+        <v>11</v>
+      </c>
+      <c r="BL89">
+        <v>16</v>
+      </c>
+      <c r="BM89">
+        <v>11</v>
+      </c>
+      <c r="BN89">
+        <v>11</v>
+      </c>
+      <c r="BO89">
+        <v>5</v>
+      </c>
+      <c r="BP89">
+        <v>1</v>
+      </c>
+      <c r="BQ89">
+        <v>30</v>
+      </c>
+      <c r="BR89">
+        <v>20</v>
+      </c>
+      <c r="BS89">
+        <v>3</v>
+      </c>
+      <c r="BT89">
+        <v>0</v>
+      </c>
+      <c r="BU89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW89">
+        <v>41</v>
+      </c>
+      <c r="BX89">
+        <v>47</v>
+      </c>
+      <c r="BY89">
+        <v>20</v>
+      </c>
+      <c r="BZ89">
+        <v>32</v>
+      </c>
+      <c r="CA89">
+        <v>21</v>
+      </c>
+      <c r="CB89">
+        <v>15</v>
+      </c>
+      <c r="CC89">
+        <v>0</v>
+      </c>
+      <c r="CD89">
+        <v>6</v>
+      </c>
+      <c r="CE89" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG89">
+        <v>0</v>
+      </c>
+      <c r="CH89">
+        <v>0</v>
+      </c>
+      <c r="CI89">
+        <v>0</v>
+      </c>
+      <c r="CJ89">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13C4D69C-E7CE-4BCB-B506-7354E671E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE96D956-CE20-403E-A9DD-353EA4F0C384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="195">
   <si>
     <t>date</t>
   </si>
@@ -619,6 +619,12 @@
   <si>
     <t>Mon 12 October, 20:30</t>
   </si>
+  <si>
+    <t>Fri 16 October, 18:00</t>
+  </si>
+  <si>
+    <t>Fri 16 October, 20:30</t>
+  </si>
 </sst>
 </file>
 
@@ -1029,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ89"/>
+  <dimension ref="A1:CJ91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1364,7 +1370,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H89" si="0">100-G2</f>
+        <f t="shared" ref="H2:H91" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -24675,6 +24681,534 @@
         <v>0</v>
       </c>
       <c r="CJ89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:88" ht="30">
+      <c r="B90" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>53</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I90">
+        <v>1.53</v>
+      </c>
+      <c r="J90">
+        <v>2.66</v>
+      </c>
+      <c r="K90">
+        <v>14</v>
+      </c>
+      <c r="L90">
+        <v>23</v>
+      </c>
+      <c r="M90">
+        <v>3</v>
+      </c>
+      <c r="N90">
+        <v>13</v>
+      </c>
+      <c r="O90">
+        <v>3</v>
+      </c>
+      <c r="P90">
+        <v>4</v>
+      </c>
+      <c r="Q90">
+        <v>2</v>
+      </c>
+      <c r="R90">
+        <v>2</v>
+      </c>
+      <c r="S90">
+        <v>457</v>
+      </c>
+      <c r="T90">
+        <v>402</v>
+      </c>
+      <c r="U90">
+        <v>9</v>
+      </c>
+      <c r="V90">
+        <v>10</v>
+      </c>
+      <c r="W90">
+        <v>5</v>
+      </c>
+      <c r="X90">
+        <v>4</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA90">
+        <v>8</v>
+      </c>
+      <c r="AB90">
+        <v>7</v>
+      </c>
+      <c r="AC90">
+        <v>3</v>
+      </c>
+      <c r="AD90">
+        <v>3</v>
+      </c>
+      <c r="AE90">
+        <v>1</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>9</v>
+      </c>
+      <c r="AH90">
+        <v>13</v>
+      </c>
+      <c r="AI90">
+        <v>5</v>
+      </c>
+      <c r="AJ90">
+        <v>10</v>
+      </c>
+      <c r="AK90">
+        <v>1.27</v>
+      </c>
+      <c r="AL90">
+        <v>1.73</v>
+      </c>
+      <c r="AM90">
+        <v>0.26</v>
+      </c>
+      <c r="AN90">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AO90">
+        <v>1.53</v>
+      </c>
+      <c r="AP90">
+        <v>1.87</v>
+      </c>
+      <c r="AQ90">
+        <v>0.8</v>
+      </c>
+      <c r="AR90">
+        <v>2.8</v>
+      </c>
+      <c r="AS90">
+        <v>530</v>
+      </c>
+      <c r="AT90">
+        <v>481</v>
+      </c>
+      <c r="AU90">
+        <v>205</v>
+      </c>
+      <c r="AV90">
+        <v>206</v>
+      </c>
+      <c r="AW90">
+        <v>252</v>
+      </c>
+      <c r="AX90">
+        <v>196</v>
+      </c>
+      <c r="AY90">
+        <v>25</v>
+      </c>
+      <c r="AZ90">
+        <v>25</v>
+      </c>
+      <c r="BA90">
+        <v>8</v>
+      </c>
+      <c r="BB90">
+        <v>7</v>
+      </c>
+      <c r="BC90">
+        <v>13</v>
+      </c>
+      <c r="BD90">
+        <v>15</v>
+      </c>
+      <c r="BE90">
+        <v>33</v>
+      </c>
+      <c r="BF90">
+        <v>26</v>
+      </c>
+      <c r="BG90">
+        <v>0</v>
+      </c>
+      <c r="BH90">
+        <v>2</v>
+      </c>
+      <c r="BI90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK90">
+        <v>9</v>
+      </c>
+      <c r="BL90">
+        <v>7</v>
+      </c>
+      <c r="BM90">
+        <v>11</v>
+      </c>
+      <c r="BN90">
+        <v>4</v>
+      </c>
+      <c r="BO90">
+        <v>2</v>
+      </c>
+      <c r="BP90">
+        <v>2</v>
+      </c>
+      <c r="BQ90">
+        <v>27</v>
+      </c>
+      <c r="BR90">
+        <v>23</v>
+      </c>
+      <c r="BS90">
+        <v>11</v>
+      </c>
+      <c r="BT90">
+        <v>2</v>
+      </c>
+      <c r="BU90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW90">
+        <v>44</v>
+      </c>
+      <c r="BX90">
+        <v>43</v>
+      </c>
+      <c r="BY90">
+        <v>30</v>
+      </c>
+      <c r="BZ90">
+        <v>27</v>
+      </c>
+      <c r="CA90">
+        <v>14</v>
+      </c>
+      <c r="CB90">
+        <v>16</v>
+      </c>
+      <c r="CC90">
+        <v>11</v>
+      </c>
+      <c r="CD90">
+        <v>13</v>
+      </c>
+      <c r="CE90" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF90" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG90">
+        <v>3</v>
+      </c>
+      <c r="CH90">
+        <v>2</v>
+      </c>
+      <c r="CI90">
+        <v>0</v>
+      </c>
+      <c r="CJ90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:88">
+      <c r="B91" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>46</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I91">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J91">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="K91">
+        <v>10</v>
+      </c>
+      <c r="L91">
+        <v>21</v>
+      </c>
+      <c r="M91">
+        <v>3</v>
+      </c>
+      <c r="N91">
+        <v>4</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>3</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>3</v>
+      </c>
+      <c r="S91">
+        <v>257</v>
+      </c>
+      <c r="T91">
+        <v>309</v>
+      </c>
+      <c r="U91">
+        <v>20</v>
+      </c>
+      <c r="V91">
+        <v>7</v>
+      </c>
+      <c r="W91">
+        <v>4</v>
+      </c>
+      <c r="X91">
+        <v>7</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA91">
+        <v>3</v>
+      </c>
+      <c r="AB91">
+        <v>11</v>
+      </c>
+      <c r="AC91">
+        <v>4</v>
+      </c>
+      <c r="AD91">
+        <v>6</v>
+      </c>
+      <c r="AE91">
+        <v>1</v>
+      </c>
+      <c r="AF91">
+        <v>1</v>
+      </c>
+      <c r="AG91">
+        <v>3</v>
+      </c>
+      <c r="AH91">
+        <v>11</v>
+      </c>
+      <c r="AI91">
+        <v>7</v>
+      </c>
+      <c r="AJ91">
+        <v>10</v>
+      </c>
+      <c r="AK91">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL91">
+        <v>1.45</v>
+      </c>
+      <c r="AM91">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN91">
+        <v>0.25</v>
+      </c>
+      <c r="AO91">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AP91">
+        <v>1.7</v>
+      </c>
+      <c r="AQ91">
+        <v>0.51</v>
+      </c>
+      <c r="AR91">
+        <v>0.32</v>
+      </c>
+      <c r="AS91">
+        <v>334</v>
+      </c>
+      <c r="AT91">
+        <v>400</v>
+      </c>
+      <c r="AU91">
+        <v>152</v>
+      </c>
+      <c r="AV91">
+        <v>151</v>
+      </c>
+      <c r="AW91">
+        <v>105</v>
+      </c>
+      <c r="AX91">
+        <v>158</v>
+      </c>
+      <c r="AY91">
+        <v>22</v>
+      </c>
+      <c r="AZ91">
+        <v>15</v>
+      </c>
+      <c r="BA91">
+        <v>2</v>
+      </c>
+      <c r="BB91">
+        <v>2</v>
+      </c>
+      <c r="BC91">
+        <v>23</v>
+      </c>
+      <c r="BD91">
+        <v>24</v>
+      </c>
+      <c r="BE91">
+        <v>16</v>
+      </c>
+      <c r="BF91">
+        <v>22</v>
+      </c>
+      <c r="BG91">
+        <v>2</v>
+      </c>
+      <c r="BH91">
+        <v>4</v>
+      </c>
+      <c r="BI91" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ91" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK91">
+        <v>20</v>
+      </c>
+      <c r="BL91">
+        <v>23</v>
+      </c>
+      <c r="BM91">
+        <v>19</v>
+      </c>
+      <c r="BN91">
+        <v>4</v>
+      </c>
+      <c r="BO91">
+        <v>5</v>
+      </c>
+      <c r="BP91">
+        <v>4</v>
+      </c>
+      <c r="BQ91">
+        <v>29</v>
+      </c>
+      <c r="BR91">
+        <v>12</v>
+      </c>
+      <c r="BS91">
+        <v>4</v>
+      </c>
+      <c r="BT91">
+        <v>3</v>
+      </c>
+      <c r="BU91" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV91" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW91">
+        <v>47</v>
+      </c>
+      <c r="BX91">
+        <v>55</v>
+      </c>
+      <c r="BY91">
+        <v>32</v>
+      </c>
+      <c r="BZ91">
+        <v>46</v>
+      </c>
+      <c r="CA91">
+        <v>15</v>
+      </c>
+      <c r="CB91">
+        <v>9</v>
+      </c>
+      <c r="CC91">
+        <v>5</v>
+      </c>
+      <c r="CD91">
+        <v>6</v>
+      </c>
+      <c r="CE91" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF91" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG91">
+        <v>4</v>
+      </c>
+      <c r="CH91">
+        <v>0</v>
+      </c>
+      <c r="CI91">
+        <v>0</v>
+      </c>
+      <c r="CJ91">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE96D956-CE20-403E-A9DD-353EA4F0C384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7029CC28-E9D3-4B6F-BDC2-9798740B824B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="201">
   <si>
     <t>date</t>
   </si>
@@ -625,6 +625,24 @@
   <si>
     <t>Fri 16 October, 20:30</t>
   </si>
+  <si>
+    <t>Sat 17 October, 14:45</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 17:30</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 20:15</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 12:15</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 14:45</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 17:30</t>
+  </si>
 </sst>
 </file>
 
@@ -1035,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ91"/>
+  <dimension ref="A1:CJ97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1370,7 +1388,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H91" si="0">100-G2</f>
+        <f t="shared" ref="H2:H97" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -25209,6 +25227,1590 @@
         <v>0</v>
       </c>
       <c r="CJ91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:88">
+      <c r="B92" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" t="s">
+        <v>99</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>66</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="I92">
+        <v>3.84</v>
+      </c>
+      <c r="J92">
+        <v>0.77</v>
+      </c>
+      <c r="K92">
+        <v>29</v>
+      </c>
+      <c r="L92">
+        <v>6</v>
+      </c>
+      <c r="M92">
+        <v>11</v>
+      </c>
+      <c r="N92">
+        <v>3</v>
+      </c>
+      <c r="O92">
+        <v>8</v>
+      </c>
+      <c r="P92">
+        <v>3</v>
+      </c>
+      <c r="Q92">
+        <v>5</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+      <c r="S92">
+        <v>401</v>
+      </c>
+      <c r="T92">
+        <v>181</v>
+      </c>
+      <c r="U92">
+        <v>12</v>
+      </c>
+      <c r="V92">
+        <v>18</v>
+      </c>
+      <c r="W92">
+        <v>10</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA92">
+        <v>10</v>
+      </c>
+      <c r="AB92">
+        <v>2</v>
+      </c>
+      <c r="AC92">
+        <v>8</v>
+      </c>
+      <c r="AD92">
+        <v>1</v>
+      </c>
+      <c r="AE92">
+        <v>0</v>
+      </c>
+      <c r="AF92">
+        <v>0</v>
+      </c>
+      <c r="AG92">
+        <v>19</v>
+      </c>
+      <c r="AH92">
+        <v>4</v>
+      </c>
+      <c r="AI92">
+        <v>10</v>
+      </c>
+      <c r="AJ92">
+        <v>2</v>
+      </c>
+      <c r="AK92">
+        <v>1.22</v>
+      </c>
+      <c r="AL92">
+        <v>0.65</v>
+      </c>
+      <c r="AM92">
+        <v>1.05</v>
+      </c>
+      <c r="AN92">
+        <v>0.12</v>
+      </c>
+      <c r="AO92">
+        <v>2.27</v>
+      </c>
+      <c r="AP92">
+        <v>0.77</v>
+      </c>
+      <c r="AQ92">
+        <v>4.3</v>
+      </c>
+      <c r="AR92">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AS92">
+        <v>477</v>
+      </c>
+      <c r="AT92">
+        <v>254</v>
+      </c>
+      <c r="AU92">
+        <v>137</v>
+      </c>
+      <c r="AV92">
+        <v>88</v>
+      </c>
+      <c r="AW92">
+        <v>264</v>
+      </c>
+      <c r="AX92">
+        <v>93</v>
+      </c>
+      <c r="AY92">
+        <v>22</v>
+      </c>
+      <c r="AZ92">
+        <v>24</v>
+      </c>
+      <c r="BA92">
+        <v>9</v>
+      </c>
+      <c r="BB92">
+        <v>1</v>
+      </c>
+      <c r="BC92">
+        <v>18</v>
+      </c>
+      <c r="BD92">
+        <v>13</v>
+      </c>
+      <c r="BE92">
+        <v>37</v>
+      </c>
+      <c r="BF92">
+        <v>11</v>
+      </c>
+      <c r="BG92">
+        <v>0</v>
+      </c>
+      <c r="BH92">
+        <v>1</v>
+      </c>
+      <c r="BI92" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ92" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK92">
+        <v>17</v>
+      </c>
+      <c r="BL92">
+        <v>11</v>
+      </c>
+      <c r="BM92">
+        <v>5</v>
+      </c>
+      <c r="BN92">
+        <v>8</v>
+      </c>
+      <c r="BO92">
+        <v>1</v>
+      </c>
+      <c r="BP92">
+        <v>8</v>
+      </c>
+      <c r="BQ92">
+        <v>13</v>
+      </c>
+      <c r="BR92">
+        <v>49</v>
+      </c>
+      <c r="BS92">
+        <v>1</v>
+      </c>
+      <c r="BT92">
+        <v>8</v>
+      </c>
+      <c r="BU92" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV92" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW92">
+        <v>59</v>
+      </c>
+      <c r="BX92">
+        <v>40</v>
+      </c>
+      <c r="BY92">
+        <v>41</v>
+      </c>
+      <c r="BZ92">
+        <v>25</v>
+      </c>
+      <c r="CA92">
+        <v>18</v>
+      </c>
+      <c r="CB92">
+        <v>15</v>
+      </c>
+      <c r="CC92">
+        <v>8</v>
+      </c>
+      <c r="CD92">
+        <v>5</v>
+      </c>
+      <c r="CE92" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF92" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG92">
+        <v>2</v>
+      </c>
+      <c r="CH92">
+        <v>3</v>
+      </c>
+      <c r="CI92">
+        <v>0</v>
+      </c>
+      <c r="CJ92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:88">
+      <c r="B93" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" t="s">
+        <v>111</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>64</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="I93">
+        <v>0.92</v>
+      </c>
+      <c r="J93">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="K93">
+        <v>19</v>
+      </c>
+      <c r="L93">
+        <v>14</v>
+      </c>
+      <c r="M93">
+        <v>4</v>
+      </c>
+      <c r="N93">
+        <v>5</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>2</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>1</v>
+      </c>
+      <c r="S93">
+        <v>493</v>
+      </c>
+      <c r="T93">
+        <v>265</v>
+      </c>
+      <c r="U93">
+        <v>9</v>
+      </c>
+      <c r="V93">
+        <v>10</v>
+      </c>
+      <c r="W93">
+        <v>6</v>
+      </c>
+      <c r="X93">
+        <v>3</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA93">
+        <v>10</v>
+      </c>
+      <c r="AB93">
+        <v>8</v>
+      </c>
+      <c r="AC93">
+        <v>5</v>
+      </c>
+      <c r="AD93">
+        <v>1</v>
+      </c>
+      <c r="AE93">
+        <v>0</v>
+      </c>
+      <c r="AF93">
+        <v>0</v>
+      </c>
+      <c r="AG93">
+        <v>14</v>
+      </c>
+      <c r="AH93">
+        <v>12</v>
+      </c>
+      <c r="AI93">
+        <v>5</v>
+      </c>
+      <c r="AJ93">
+        <v>2</v>
+      </c>
+      <c r="AK93">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AL93">
+        <v>1.39</v>
+      </c>
+      <c r="AM93">
+        <v>0.34</v>
+      </c>
+      <c r="AN93">
+        <v>0.65</v>
+      </c>
+      <c r="AO93">
+        <v>0.92</v>
+      </c>
+      <c r="AP93">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AQ93">
+        <v>0.9</v>
+      </c>
+      <c r="AR93">
+        <v>2.64</v>
+      </c>
+      <c r="AS93">
+        <v>566</v>
+      </c>
+      <c r="AT93">
+        <v>329</v>
+      </c>
+      <c r="AU93">
+        <v>245</v>
+      </c>
+      <c r="AV93">
+        <v>152</v>
+      </c>
+      <c r="AW93">
+        <v>248</v>
+      </c>
+      <c r="AX93">
+        <v>113</v>
+      </c>
+      <c r="AY93">
+        <v>22</v>
+      </c>
+      <c r="AZ93">
+        <v>21</v>
+      </c>
+      <c r="BA93">
+        <v>9</v>
+      </c>
+      <c r="BB93">
+        <v>3</v>
+      </c>
+      <c r="BC93">
+        <v>22</v>
+      </c>
+      <c r="BD93">
+        <v>11</v>
+      </c>
+      <c r="BE93">
+        <v>36</v>
+      </c>
+      <c r="BF93">
+        <v>25</v>
+      </c>
+      <c r="BG93">
+        <v>1</v>
+      </c>
+      <c r="BH93">
+        <v>4</v>
+      </c>
+      <c r="BI93" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ93" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK93">
+        <v>12</v>
+      </c>
+      <c r="BL93">
+        <v>16</v>
+      </c>
+      <c r="BM93">
+        <v>7</v>
+      </c>
+      <c r="BN93">
+        <v>10</v>
+      </c>
+      <c r="BO93">
+        <v>1</v>
+      </c>
+      <c r="BP93">
+        <v>5</v>
+      </c>
+      <c r="BQ93">
+        <v>15</v>
+      </c>
+      <c r="BR93">
+        <v>33</v>
+      </c>
+      <c r="BS93">
+        <v>4</v>
+      </c>
+      <c r="BT93">
+        <v>4</v>
+      </c>
+      <c r="BU93" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV93" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW93">
+        <v>50</v>
+      </c>
+      <c r="BX93">
+        <v>54</v>
+      </c>
+      <c r="BY93">
+        <v>33</v>
+      </c>
+      <c r="BZ93">
+        <v>40</v>
+      </c>
+      <c r="CA93">
+        <v>17</v>
+      </c>
+      <c r="CB93">
+        <v>14</v>
+      </c>
+      <c r="CC93">
+        <v>11</v>
+      </c>
+      <c r="CD93">
+        <v>17</v>
+      </c>
+      <c r="CE93" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF93" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG93">
+        <v>1</v>
+      </c>
+      <c r="CH93">
+        <v>1</v>
+      </c>
+      <c r="CI93">
+        <v>0</v>
+      </c>
+      <c r="CJ93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:88" ht="30">
+      <c r="B94" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" t="s">
+        <v>102</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>52</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="I94">
+        <v>0.85</v>
+      </c>
+      <c r="J94">
+        <v>0.63</v>
+      </c>
+      <c r="K94">
+        <v>14</v>
+      </c>
+      <c r="L94">
+        <v>14</v>
+      </c>
+      <c r="M94">
+        <v>3</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>387</v>
+      </c>
+      <c r="T94">
+        <v>355</v>
+      </c>
+      <c r="U94">
+        <v>21</v>
+      </c>
+      <c r="V94">
+        <v>14</v>
+      </c>
+      <c r="W94">
+        <v>5</v>
+      </c>
+      <c r="X94">
+        <v>3</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA94">
+        <v>8</v>
+      </c>
+      <c r="AB94">
+        <v>7</v>
+      </c>
+      <c r="AC94">
+        <v>3</v>
+      </c>
+      <c r="AD94">
+        <v>5</v>
+      </c>
+      <c r="AE94">
+        <v>0</v>
+      </c>
+      <c r="AF94">
+        <v>0</v>
+      </c>
+      <c r="AG94">
+        <v>9</v>
+      </c>
+      <c r="AH94">
+        <v>9</v>
+      </c>
+      <c r="AI94">
+        <v>5</v>
+      </c>
+      <c r="AJ94">
+        <v>5</v>
+      </c>
+      <c r="AK94">
+        <v>0.62</v>
+      </c>
+      <c r="AL94">
+        <v>0.5</v>
+      </c>
+      <c r="AM94">
+        <v>0.22</v>
+      </c>
+      <c r="AN94">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AO94">
+        <v>0.85</v>
+      </c>
+      <c r="AP94">
+        <v>0.63</v>
+      </c>
+      <c r="AQ94">
+        <v>0.59</v>
+      </c>
+      <c r="AR94">
+        <v>0.44</v>
+      </c>
+      <c r="AS94">
+        <v>451</v>
+      </c>
+      <c r="AT94">
+        <v>424</v>
+      </c>
+      <c r="AU94">
+        <v>130</v>
+      </c>
+      <c r="AV94">
+        <v>170</v>
+      </c>
+      <c r="AW94">
+        <v>257</v>
+      </c>
+      <c r="AX94">
+        <v>185</v>
+      </c>
+      <c r="AY94">
+        <v>23</v>
+      </c>
+      <c r="AZ94">
+        <v>24</v>
+      </c>
+      <c r="BA94">
+        <v>4</v>
+      </c>
+      <c r="BB94">
+        <v>6</v>
+      </c>
+      <c r="BC94">
+        <v>13</v>
+      </c>
+      <c r="BD94">
+        <v>18</v>
+      </c>
+      <c r="BE94">
+        <v>26</v>
+      </c>
+      <c r="BF94">
+        <v>20</v>
+      </c>
+      <c r="BG94">
+        <v>0</v>
+      </c>
+      <c r="BH94">
+        <v>2</v>
+      </c>
+      <c r="BI94" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ94" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK94">
+        <v>19</v>
+      </c>
+      <c r="BL94">
+        <v>20</v>
+      </c>
+      <c r="BM94">
+        <v>6</v>
+      </c>
+      <c r="BN94">
+        <v>6</v>
+      </c>
+      <c r="BO94">
+        <v>5</v>
+      </c>
+      <c r="BP94">
+        <v>3</v>
+      </c>
+      <c r="BQ94">
+        <v>26</v>
+      </c>
+      <c r="BR94">
+        <v>29</v>
+      </c>
+      <c r="BS94">
+        <v>1</v>
+      </c>
+      <c r="BT94">
+        <v>2</v>
+      </c>
+      <c r="BU94" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV94" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW94">
+        <v>54</v>
+      </c>
+      <c r="BX94">
+        <v>62</v>
+      </c>
+      <c r="BY94">
+        <v>40</v>
+      </c>
+      <c r="BZ94">
+        <v>47</v>
+      </c>
+      <c r="CA94">
+        <v>14</v>
+      </c>
+      <c r="CB94">
+        <v>15</v>
+      </c>
+      <c r="CC94">
+        <v>8</v>
+      </c>
+      <c r="CD94">
+        <v>6</v>
+      </c>
+      <c r="CE94" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF94" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG94">
+        <v>1</v>
+      </c>
+      <c r="CH94">
+        <v>1</v>
+      </c>
+      <c r="CI94">
+        <v>0</v>
+      </c>
+      <c r="CJ94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:88">
+      <c r="B95" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95" t="s">
+        <v>114</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>53</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I95">
+        <v>3.08</v>
+      </c>
+      <c r="J95">
+        <v>0.86</v>
+      </c>
+      <c r="K95">
+        <v>27</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+      <c r="M95">
+        <v>5</v>
+      </c>
+      <c r="N95">
+        <v>3</v>
+      </c>
+      <c r="O95">
+        <v>2</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>417</v>
+      </c>
+      <c r="T95">
+        <v>349</v>
+      </c>
+      <c r="U95">
+        <v>9</v>
+      </c>
+      <c r="V95">
+        <v>9</v>
+      </c>
+      <c r="W95">
+        <v>10</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA95">
+        <v>9</v>
+      </c>
+      <c r="AB95">
+        <v>3</v>
+      </c>
+      <c r="AC95">
+        <v>13</v>
+      </c>
+      <c r="AD95">
+        <v>4</v>
+      </c>
+      <c r="AE95">
+        <v>1</v>
+      </c>
+      <c r="AF95">
+        <v>0</v>
+      </c>
+      <c r="AG95">
+        <v>17</v>
+      </c>
+      <c r="AH95">
+        <v>7</v>
+      </c>
+      <c r="AI95">
+        <v>10</v>
+      </c>
+      <c r="AJ95">
+        <v>3</v>
+      </c>
+      <c r="AK95">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AL95">
+        <v>0.7</v>
+      </c>
+      <c r="AM95">
+        <v>0.86</v>
+      </c>
+      <c r="AN95">
+        <v>0.15</v>
+      </c>
+      <c r="AO95">
+        <v>3.08</v>
+      </c>
+      <c r="AP95">
+        <v>0.86</v>
+      </c>
+      <c r="AQ95">
+        <v>1.63</v>
+      </c>
+      <c r="AR95">
+        <v>1.31</v>
+      </c>
+      <c r="AS95">
+        <v>485</v>
+      </c>
+      <c r="AT95">
+        <v>439</v>
+      </c>
+      <c r="AU95">
+        <v>129</v>
+      </c>
+      <c r="AV95">
+        <v>212</v>
+      </c>
+      <c r="AW95">
+        <v>288</v>
+      </c>
+      <c r="AX95">
+        <v>137</v>
+      </c>
+      <c r="AY95">
+        <v>20</v>
+      </c>
+      <c r="AZ95">
+        <v>24</v>
+      </c>
+      <c r="BA95">
+        <v>11</v>
+      </c>
+      <c r="BB95">
+        <v>2</v>
+      </c>
+      <c r="BC95">
+        <v>28</v>
+      </c>
+      <c r="BD95">
+        <v>19</v>
+      </c>
+      <c r="BE95">
+        <v>46</v>
+      </c>
+      <c r="BF95">
+        <v>11</v>
+      </c>
+      <c r="BG95">
+        <v>0</v>
+      </c>
+      <c r="BH95">
+        <v>0</v>
+      </c>
+      <c r="BI95" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ95" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK95">
+        <v>18</v>
+      </c>
+      <c r="BL95">
+        <v>17</v>
+      </c>
+      <c r="BM95">
+        <v>17</v>
+      </c>
+      <c r="BN95">
+        <v>5</v>
+      </c>
+      <c r="BO95">
+        <v>4</v>
+      </c>
+      <c r="BP95">
+        <v>11</v>
+      </c>
+      <c r="BQ95">
+        <v>24</v>
+      </c>
+      <c r="BR95">
+        <v>32</v>
+      </c>
+      <c r="BS95">
+        <v>2</v>
+      </c>
+      <c r="BT95">
+        <v>4</v>
+      </c>
+      <c r="BU95" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV95" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW95">
+        <v>51</v>
+      </c>
+      <c r="BX95">
+        <v>42</v>
+      </c>
+      <c r="BY95">
+        <v>31</v>
+      </c>
+      <c r="BZ95">
+        <v>31</v>
+      </c>
+      <c r="CA95">
+        <v>20</v>
+      </c>
+      <c r="CB95">
+        <v>11</v>
+      </c>
+      <c r="CC95">
+        <v>4</v>
+      </c>
+      <c r="CD95">
+        <v>6</v>
+      </c>
+      <c r="CE95" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF95" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG95">
+        <v>0</v>
+      </c>
+      <c r="CH95">
+        <v>2</v>
+      </c>
+      <c r="CI95">
+        <v>0</v>
+      </c>
+      <c r="CJ95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:88" ht="30">
+      <c r="B96" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>36</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="I96">
+        <v>1.93</v>
+      </c>
+      <c r="J96">
+        <v>1.43</v>
+      </c>
+      <c r="K96">
+        <v>12</v>
+      </c>
+      <c r="L96">
+        <v>15</v>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96">
+        <v>3</v>
+      </c>
+      <c r="P96">
+        <v>4</v>
+      </c>
+      <c r="Q96">
+        <v>2</v>
+      </c>
+      <c r="R96">
+        <v>4</v>
+      </c>
+      <c r="S96">
+        <v>180</v>
+      </c>
+      <c r="T96">
+        <v>406</v>
+      </c>
+      <c r="U96">
+        <v>11</v>
+      </c>
+      <c r="V96">
+        <v>13</v>
+      </c>
+      <c r="W96">
+        <v>5</v>
+      </c>
+      <c r="X96">
+        <v>3</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA96">
+        <v>6</v>
+      </c>
+      <c r="AB96">
+        <v>9</v>
+      </c>
+      <c r="AC96">
+        <v>2</v>
+      </c>
+      <c r="AD96">
+        <v>3</v>
+      </c>
+      <c r="AE96">
+        <v>2</v>
+      </c>
+      <c r="AF96">
+        <v>1</v>
+      </c>
+      <c r="AG96">
+        <v>9</v>
+      </c>
+      <c r="AH96">
+        <v>10</v>
+      </c>
+      <c r="AI96">
+        <v>3</v>
+      </c>
+      <c r="AJ96">
+        <v>5</v>
+      </c>
+      <c r="AK96">
+        <v>0.91</v>
+      </c>
+      <c r="AL96">
+        <v>1.43</v>
+      </c>
+      <c r="AM96">
+        <v>0.23</v>
+      </c>
+      <c r="AN96">
+        <v>0</v>
+      </c>
+      <c r="AO96">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AP96">
+        <v>1.43</v>
+      </c>
+      <c r="AQ96">
+        <v>1.37</v>
+      </c>
+      <c r="AR96">
+        <v>0.45</v>
+      </c>
+      <c r="AS96">
+        <v>270</v>
+      </c>
+      <c r="AT96">
+        <v>512</v>
+      </c>
+      <c r="AU96">
+        <v>100</v>
+      </c>
+      <c r="AV96">
+        <v>173</v>
+      </c>
+      <c r="AW96">
+        <v>80</v>
+      </c>
+      <c r="AX96">
+        <v>233</v>
+      </c>
+      <c r="AY96">
+        <v>29</v>
+      </c>
+      <c r="AZ96">
+        <v>9</v>
+      </c>
+      <c r="BA96">
+        <v>5</v>
+      </c>
+      <c r="BB96">
+        <v>8</v>
+      </c>
+      <c r="BC96">
+        <v>10</v>
+      </c>
+      <c r="BD96">
+        <v>23</v>
+      </c>
+      <c r="BE96">
+        <v>27</v>
+      </c>
+      <c r="BF96">
+        <v>25</v>
+      </c>
+      <c r="BG96">
+        <v>1</v>
+      </c>
+      <c r="BH96">
+        <v>0</v>
+      </c>
+      <c r="BI96" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ96" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK96">
+        <v>20</v>
+      </c>
+      <c r="BL96">
+        <v>16</v>
+      </c>
+      <c r="BM96">
+        <v>9</v>
+      </c>
+      <c r="BN96">
+        <v>4</v>
+      </c>
+      <c r="BO96">
+        <v>3</v>
+      </c>
+      <c r="BP96">
+        <v>2</v>
+      </c>
+      <c r="BQ96">
+        <v>29</v>
+      </c>
+      <c r="BR96">
+        <v>22</v>
+      </c>
+      <c r="BS96">
+        <v>3</v>
+      </c>
+      <c r="BT96">
+        <v>2</v>
+      </c>
+      <c r="BU96" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV96" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW96">
+        <v>57</v>
+      </c>
+      <c r="BX96">
+        <v>57</v>
+      </c>
+      <c r="BY96">
+        <v>37</v>
+      </c>
+      <c r="BZ96">
+        <v>34</v>
+      </c>
+      <c r="CA96">
+        <v>20</v>
+      </c>
+      <c r="CB96">
+        <v>23</v>
+      </c>
+      <c r="CC96">
+        <v>5</v>
+      </c>
+      <c r="CD96">
+        <v>7</v>
+      </c>
+      <c r="CE96" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF96" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG96">
+        <v>2</v>
+      </c>
+      <c r="CH96">
+        <v>1</v>
+      </c>
+      <c r="CI96">
+        <v>0</v>
+      </c>
+      <c r="CJ96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:88">
+      <c r="B97" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" t="s">
+        <v>96</v>
+      </c>
+      <c r="E97">
+        <v>6</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>60</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="I97">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J97">
+        <v>1.19</v>
+      </c>
+      <c r="K97">
+        <v>14</v>
+      </c>
+      <c r="L97">
+        <v>15</v>
+      </c>
+      <c r="M97">
+        <v>6</v>
+      </c>
+      <c r="N97">
+        <v>5</v>
+      </c>
+      <c r="O97">
+        <v>7</v>
+      </c>
+      <c r="P97">
+        <v>1</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="S97">
+        <v>466</v>
+      </c>
+      <c r="T97">
+        <v>281</v>
+      </c>
+      <c r="U97">
+        <v>13</v>
+      </c>
+      <c r="V97">
+        <v>13</v>
+      </c>
+      <c r="W97">
+        <v>5</v>
+      </c>
+      <c r="X97">
+        <v>7</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA97">
+        <v>5</v>
+      </c>
+      <c r="AB97">
+        <v>7</v>
+      </c>
+      <c r="AC97">
+        <v>3</v>
+      </c>
+      <c r="AD97">
+        <v>3</v>
+      </c>
+      <c r="AE97">
+        <v>0</v>
+      </c>
+      <c r="AF97">
+        <v>0</v>
+      </c>
+      <c r="AG97">
+        <v>10</v>
+      </c>
+      <c r="AH97">
+        <v>7</v>
+      </c>
+      <c r="AI97">
+        <v>4</v>
+      </c>
+      <c r="AJ97">
+        <v>8</v>
+      </c>
+      <c r="AK97">
+        <v>1.97</v>
+      </c>
+      <c r="AL97">
+        <v>0.99</v>
+      </c>
+      <c r="AM97">
+        <v>0.27</v>
+      </c>
+      <c r="AN97">
+        <v>0.21</v>
+      </c>
+      <c r="AO97">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AP97">
+        <v>1.19</v>
+      </c>
+      <c r="AQ97">
+        <v>3.2</v>
+      </c>
+      <c r="AR97">
+        <v>1.31</v>
+      </c>
+      <c r="AS97">
+        <v>530</v>
+      </c>
+      <c r="AT97">
+        <v>340</v>
+      </c>
+      <c r="AU97">
+        <v>274</v>
+      </c>
+      <c r="AV97">
+        <v>150</v>
+      </c>
+      <c r="AW97">
+        <v>192</v>
+      </c>
+      <c r="AX97">
+        <v>131</v>
+      </c>
+      <c r="AY97">
+        <v>13</v>
+      </c>
+      <c r="AZ97">
+        <v>24</v>
+      </c>
+      <c r="BA97">
+        <v>4</v>
+      </c>
+      <c r="BB97">
+        <v>3</v>
+      </c>
+      <c r="BC97">
+        <v>13</v>
+      </c>
+      <c r="BD97">
+        <v>17</v>
+      </c>
+      <c r="BE97">
+        <v>38</v>
+      </c>
+      <c r="BF97">
+        <v>27</v>
+      </c>
+      <c r="BG97">
+        <v>0</v>
+      </c>
+      <c r="BH97">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ97" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK97">
+        <v>17</v>
+      </c>
+      <c r="BL97">
+        <v>15</v>
+      </c>
+      <c r="BM97">
+        <v>9</v>
+      </c>
+      <c r="BN97">
+        <v>12</v>
+      </c>
+      <c r="BO97">
+        <v>4</v>
+      </c>
+      <c r="BP97">
+        <v>3</v>
+      </c>
+      <c r="BQ97">
+        <v>23</v>
+      </c>
+      <c r="BR97">
+        <v>24</v>
+      </c>
+      <c r="BS97">
+        <v>3</v>
+      </c>
+      <c r="BT97">
+        <v>0</v>
+      </c>
+      <c r="BU97" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV97" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW97">
+        <v>45</v>
+      </c>
+      <c r="BX97">
+        <v>40</v>
+      </c>
+      <c r="BY97">
+        <v>34</v>
+      </c>
+      <c r="BZ97">
+        <v>35</v>
+      </c>
+      <c r="CA97">
+        <v>11</v>
+      </c>
+      <c r="CB97">
+        <v>5</v>
+      </c>
+      <c r="CC97">
+        <v>5</v>
+      </c>
+      <c r="CD97">
+        <v>7</v>
+      </c>
+      <c r="CE97" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF97" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG97">
+        <v>2</v>
+      </c>
+      <c r="CH97">
+        <v>3</v>
+      </c>
+      <c r="CI97">
+        <v>0</v>
+      </c>
+      <c r="CJ97">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7029CC28-E9D3-4B6F-BDC2-9798740B824B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A341ED-5BE6-4409-92E8-DDDC89C47253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="204">
   <si>
     <t>date</t>
   </si>
@@ -643,6 +643,15 @@
   <si>
     <t>Sun 18 October, 17:30</t>
   </si>
+  <si>
+    <t>Mon 19 October, 19:00</t>
+  </si>
+  <si>
+    <t>Fri 23 October, 18:00</t>
+  </si>
+  <si>
+    <t>Fri 23 October, 20:30</t>
+  </si>
 </sst>
 </file>
 
@@ -1053,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ97"/>
+  <dimension ref="A1:CJ100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1388,7 +1397,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H97" si="0">100-G2</f>
+        <f t="shared" ref="H2:H100" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -10711,6 +10720,9 @@
       </c>
     </row>
     <row r="37" spans="1:88" ht="30">
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="B37" s="4" t="s">
         <v>141</v>
       </c>
@@ -10975,6 +10987,9 @@
       </c>
     </row>
     <row r="38" spans="1:88">
+      <c r="A38">
+        <v>37</v>
+      </c>
       <c r="B38" s="4" t="s">
         <v>142</v>
       </c>
@@ -11239,6 +11254,9 @@
       </c>
     </row>
     <row r="39" spans="1:88">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" s="4" t="s">
         <v>143</v>
       </c>
@@ -11503,6 +11521,9 @@
       </c>
     </row>
     <row r="40" spans="1:88">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" s="4" t="s">
         <v>144</v>
       </c>
@@ -11767,6 +11788,9 @@
       </c>
     </row>
     <row r="41" spans="1:88" ht="30">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" s="4" t="s">
         <v>145</v>
       </c>
@@ -12031,6 +12055,9 @@
       </c>
     </row>
     <row r="42" spans="1:88" ht="30">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" s="2" t="s">
         <v>146</v>
       </c>
@@ -12295,6 +12322,9 @@
       </c>
     </row>
     <row r="43" spans="1:88">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" s="2" t="s">
         <v>147</v>
       </c>
@@ -12559,6 +12589,9 @@
       </c>
     </row>
     <row r="44" spans="1:88" ht="30">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" s="2" t="s">
         <v>148</v>
       </c>
@@ -12823,6 +12856,9 @@
       </c>
     </row>
     <row r="45" spans="1:88">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
@@ -13087,6 +13123,9 @@
       </c>
     </row>
     <row r="46" spans="1:88" ht="30">
+      <c r="A46">
+        <v>45</v>
+      </c>
       <c r="B46" s="4" t="s">
         <v>150</v>
       </c>
@@ -13351,6 +13390,9 @@
       </c>
     </row>
     <row r="47" spans="1:88">
+      <c r="A47">
+        <v>46</v>
+      </c>
       <c r="B47" s="4" t="s">
         <v>151</v>
       </c>
@@ -13615,6 +13657,9 @@
       </c>
     </row>
     <row r="48" spans="1:88">
+      <c r="A48">
+        <v>47</v>
+      </c>
       <c r="B48" s="4" t="s">
         <v>152</v>
       </c>
@@ -13878,7 +13923,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:88" ht="30">
+    <row r="49" spans="1:88" ht="30">
+      <c r="A49">
+        <v>48</v>
+      </c>
       <c r="B49" s="4" t="s">
         <v>153</v>
       </c>
@@ -14142,7 +14190,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:88" ht="30">
+    <row r="50" spans="1:88" ht="30">
+      <c r="A50">
+        <v>49</v>
+      </c>
       <c r="B50" s="4" t="s">
         <v>154</v>
       </c>
@@ -14406,7 +14457,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:88" ht="25.5">
+    <row r="51" spans="1:88" ht="25.5">
+      <c r="A51">
+        <v>50</v>
+      </c>
       <c r="B51" s="4" t="s">
         <v>155</v>
       </c>
@@ -14670,7 +14724,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:88" ht="30">
+    <row r="52" spans="1:88" ht="30">
+      <c r="A52">
+        <v>51</v>
+      </c>
       <c r="B52" s="4" t="s">
         <v>156</v>
       </c>
@@ -14934,7 +14991,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:88" ht="25.5">
+    <row r="53" spans="1:88" ht="25.5">
+      <c r="A53">
+        <v>52</v>
+      </c>
       <c r="B53" s="4" t="s">
         <v>157</v>
       </c>
@@ -15198,7 +15258,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:88" ht="30">
+    <row r="54" spans="1:88" ht="30">
+      <c r="A54">
+        <v>53</v>
+      </c>
       <c r="B54" s="4" t="s">
         <v>158</v>
       </c>
@@ -15462,7 +15525,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:88" ht="25.5">
+    <row r="55" spans="1:88" ht="25.5">
+      <c r="A55">
+        <v>54</v>
+      </c>
       <c r="B55" s="4" t="s">
         <v>159</v>
       </c>
@@ -15726,7 +15792,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:88" ht="30">
+    <row r="56" spans="1:88" ht="30">
+      <c r="A56">
+        <v>55</v>
+      </c>
       <c r="B56" s="4" t="s">
         <v>160</v>
       </c>
@@ -15990,7 +16059,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:88" ht="32.25" customHeight="1">
+    <row r="57" spans="1:88" ht="32.25" customHeight="1">
+      <c r="A57">
+        <v>56</v>
+      </c>
       <c r="B57" s="4" t="s">
         <v>161</v>
       </c>
@@ -16254,7 +16326,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:88" ht="30">
+    <row r="58" spans="1:88" ht="30">
+      <c r="A58">
+        <v>57</v>
+      </c>
       <c r="B58" s="4" t="s">
         <v>162</v>
       </c>
@@ -16518,7 +16593,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:88" ht="25.5">
+    <row r="59" spans="1:88" ht="25.5">
+      <c r="A59">
+        <v>58</v>
+      </c>
       <c r="B59" s="4" t="s">
         <v>163</v>
       </c>
@@ -16782,7 +16860,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:88" ht="30">
+    <row r="60" spans="1:88" ht="30">
+      <c r="A60">
+        <v>59</v>
+      </c>
       <c r="B60" s="4" t="s">
         <v>164</v>
       </c>
@@ -17046,7 +17127,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:88" ht="30">
+    <row r="61" spans="1:88" ht="30">
+      <c r="A61">
+        <v>60</v>
+      </c>
       <c r="B61" s="4" t="s">
         <v>165</v>
       </c>
@@ -17310,7 +17394,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:88" ht="25.5">
+    <row r="62" spans="1:88" ht="25.5">
+      <c r="A62">
+        <v>61</v>
+      </c>
       <c r="B62" s="4" t="s">
         <v>166</v>
       </c>
@@ -17574,7 +17661,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:88" ht="25.5">
+    <row r="63" spans="1:88" ht="25.5">
+      <c r="A63">
+        <v>62</v>
+      </c>
       <c r="B63" s="4" t="s">
         <v>167</v>
       </c>
@@ -17838,7 +17928,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:88" ht="25.5">
+    <row r="64" spans="1:88" ht="25.5">
+      <c r="A64">
+        <v>63</v>
+      </c>
       <c r="B64" s="4" t="s">
         <v>168</v>
       </c>
@@ -18102,7 +18195,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:88" ht="25.5">
+    <row r="65" spans="1:88" ht="25.5">
+      <c r="A65">
+        <v>64</v>
+      </c>
       <c r="B65" s="4" t="s">
         <v>169</v>
       </c>
@@ -18366,7 +18462,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:88" ht="30">
+    <row r="66" spans="1:88" ht="30">
+      <c r="A66">
+        <v>65</v>
+      </c>
       <c r="B66" s="4" t="s">
         <v>170</v>
       </c>
@@ -18630,7 +18729,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:88" ht="30">
+    <row r="67" spans="1:88" ht="30">
+      <c r="A67">
+        <v>66</v>
+      </c>
       <c r="B67" s="4" t="s">
         <v>171</v>
       </c>
@@ -18894,7 +18996,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:88" ht="30">
+    <row r="68" spans="1:88" ht="30">
+      <c r="A68">
+        <v>67</v>
+      </c>
       <c r="B68" s="4" t="s">
         <v>172</v>
       </c>
@@ -19158,7 +19263,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:88" ht="30">
+    <row r="69" spans="1:88" ht="30">
+      <c r="A69">
+        <v>68</v>
+      </c>
       <c r="B69" s="4" t="s">
         <v>173</v>
       </c>
@@ -19422,7 +19530,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:88" ht="25.5">
+    <row r="70" spans="1:88" ht="25.5">
+      <c r="A70">
+        <v>69</v>
+      </c>
       <c r="B70" s="4" t="s">
         <v>174</v>
       </c>
@@ -19686,7 +19797,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:88" ht="30">
+    <row r="71" spans="1:88" ht="30">
+      <c r="A71">
+        <v>70</v>
+      </c>
       <c r="B71" s="4" t="s">
         <v>175</v>
       </c>
@@ -19950,7 +20064,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:88" ht="25.5">
+    <row r="72" spans="1:88" ht="25.5">
+      <c r="A72">
+        <v>71</v>
+      </c>
       <c r="B72" s="4" t="s">
         <v>175</v>
       </c>
@@ -20214,7 +20331,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:88" ht="30">
+    <row r="73" spans="1:88" ht="30">
+      <c r="A73">
+        <v>72</v>
+      </c>
       <c r="B73" s="4" t="s">
         <v>176</v>
       </c>
@@ -20478,7 +20598,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:88" ht="25.5">
+    <row r="74" spans="1:88" ht="25.5">
+      <c r="A74">
+        <v>73</v>
+      </c>
       <c r="B74" s="4" t="s">
         <v>177</v>
       </c>
@@ -20742,7 +20865,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:88" ht="25.5">
+    <row r="75" spans="1:88" ht="25.5">
+      <c r="A75">
+        <v>74</v>
+      </c>
       <c r="B75" s="4" t="s">
         <v>178</v>
       </c>
@@ -21006,7 +21132,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:88" ht="25.5">
+    <row r="76" spans="1:88" ht="25.5">
+      <c r="A76">
+        <v>75</v>
+      </c>
       <c r="B76" s="4" t="s">
         <v>179</v>
       </c>
@@ -21270,7 +21399,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:88" ht="25.5">
+    <row r="77" spans="1:88" ht="25.5">
+      <c r="A77">
+        <v>76</v>
+      </c>
       <c r="B77" s="4" t="s">
         <v>180</v>
       </c>
@@ -21534,7 +21666,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:88" ht="30">
+    <row r="78" spans="1:88" ht="30">
+      <c r="A78">
+        <v>77</v>
+      </c>
       <c r="B78" s="4" t="s">
         <v>181</v>
       </c>
@@ -21798,7 +21933,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:88" ht="30">
+    <row r="79" spans="1:88" ht="30">
+      <c r="A79">
+        <v>78</v>
+      </c>
       <c r="B79" s="4" t="s">
         <v>182</v>
       </c>
@@ -22062,7 +22200,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:88" ht="30">
+    <row r="80" spans="1:88" ht="30">
+      <c r="A80">
+        <v>79</v>
+      </c>
       <c r="B80" s="8" t="s">
         <v>183</v>
       </c>
@@ -22326,7 +22467,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:88" ht="30">
+    <row r="81" spans="1:88" ht="30">
+      <c r="A81">
+        <v>80</v>
+      </c>
       <c r="B81" s="8" t="s">
         <v>184</v>
       </c>
@@ -22590,7 +22734,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:88">
+    <row r="82" spans="1:88">
+      <c r="A82">
+        <v>81</v>
+      </c>
       <c r="B82" s="7" t="s">
         <v>185</v>
       </c>
@@ -22854,7 +23001,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:88">
+    <row r="83" spans="1:88">
+      <c r="A83">
+        <v>82</v>
+      </c>
       <c r="B83" s="7" t="s">
         <v>186</v>
       </c>
@@ -23118,7 +23268,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:88" ht="30">
+    <row r="84" spans="1:88" ht="30">
+      <c r="A84">
+        <v>83</v>
+      </c>
       <c r="B84" s="7" t="s">
         <v>187</v>
       </c>
@@ -23382,7 +23535,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:88">
+    <row r="85" spans="1:88">
+      <c r="A85">
+        <v>84</v>
+      </c>
       <c r="B85" s="4" t="s">
         <v>188</v>
       </c>
@@ -23646,7 +23802,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:88">
+    <row r="86" spans="1:88">
+      <c r="A86">
+        <v>85</v>
+      </c>
       <c r="B86" s="4" t="s">
         <v>189</v>
       </c>
@@ -23910,7 +24069,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:88" ht="30">
+    <row r="87" spans="1:88" ht="30">
+      <c r="A87">
+        <v>86</v>
+      </c>
       <c r="B87" s="4" t="s">
         <v>190</v>
       </c>
@@ -24174,7 +24336,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:88" ht="30">
+    <row r="88" spans="1:88" ht="30">
+      <c r="A88">
+        <v>87</v>
+      </c>
       <c r="B88" s="4" t="s">
         <v>191</v>
       </c>
@@ -24438,7 +24603,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:88" ht="30">
+    <row r="89" spans="1:88" ht="30">
+      <c r="A89">
+        <v>88</v>
+      </c>
       <c r="B89" s="4" t="s">
         <v>192</v>
       </c>
@@ -24702,7 +24870,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:88" ht="30">
+    <row r="90" spans="1:88" ht="30">
+      <c r="A90">
+        <v>89</v>
+      </c>
       <c r="B90" s="4" t="s">
         <v>193</v>
       </c>
@@ -24966,7 +25137,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:88">
+    <row r="91" spans="1:88">
+      <c r="A91">
+        <v>90</v>
+      </c>
       <c r="B91" s="4" t="s">
         <v>194</v>
       </c>
@@ -25230,7 +25404,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:88">
+    <row r="92" spans="1:88">
+      <c r="A92">
+        <v>91</v>
+      </c>
       <c r="B92" s="4" t="s">
         <v>195</v>
       </c>
@@ -25494,7 +25671,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:88">
+    <row r="93" spans="1:88">
+      <c r="A93">
+        <v>92</v>
+      </c>
       <c r="B93" s="4" t="s">
         <v>196</v>
       </c>
@@ -25758,7 +25938,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:88" ht="30">
+    <row r="94" spans="1:88" ht="30">
+      <c r="A94">
+        <v>93</v>
+      </c>
       <c r="B94" s="4" t="s">
         <v>197</v>
       </c>
@@ -26022,7 +26205,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:88">
+    <row r="95" spans="1:88">
+      <c r="A95">
+        <v>94</v>
+      </c>
       <c r="B95" s="4" t="s">
         <v>198</v>
       </c>
@@ -26286,7 +26472,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:88" ht="30">
+    <row r="96" spans="1:88" ht="30">
+      <c r="A96">
+        <v>95</v>
+      </c>
       <c r="B96" s="4" t="s">
         <v>199</v>
       </c>
@@ -26550,7 +26739,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:88">
+    <row r="97" spans="1:88">
+      <c r="A97">
+        <v>96</v>
+      </c>
       <c r="B97" s="4" t="s">
         <v>200</v>
       </c>
@@ -26811,6 +27003,798 @@
         <v>0</v>
       </c>
       <c r="CJ97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:88" ht="30">
+      <c r="B98" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>46</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I98">
+        <v>0.46</v>
+      </c>
+      <c r="J98">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K98">
+        <v>5</v>
+      </c>
+      <c r="L98">
+        <v>16</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>1</v>
+      </c>
+      <c r="P98">
+        <v>2</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98">
+        <v>353</v>
+      </c>
+      <c r="T98">
+        <v>430</v>
+      </c>
+      <c r="U98">
+        <v>18</v>
+      </c>
+      <c r="V98">
+        <v>11</v>
+      </c>
+      <c r="W98">
+        <v>2</v>
+      </c>
+      <c r="X98">
+        <v>6</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA98">
+        <v>2</v>
+      </c>
+      <c r="AB98">
+        <v>9</v>
+      </c>
+      <c r="AC98">
+        <v>2</v>
+      </c>
+      <c r="AD98">
+        <v>6</v>
+      </c>
+      <c r="AE98">
+        <v>0</v>
+      </c>
+      <c r="AF98">
+        <v>0</v>
+      </c>
+      <c r="AG98">
+        <v>4</v>
+      </c>
+      <c r="AH98">
+        <v>12</v>
+      </c>
+      <c r="AI98">
+        <v>1</v>
+      </c>
+      <c r="AJ98">
+        <v>4</v>
+      </c>
+      <c r="AK98">
+        <v>0.46</v>
+      </c>
+      <c r="AL98">
+        <v>0.85</v>
+      </c>
+      <c r="AM98">
+        <v>0</v>
+      </c>
+      <c r="AN98">
+        <v>0.27</v>
+      </c>
+      <c r="AO98">
+        <v>0.46</v>
+      </c>
+      <c r="AP98">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AQ98">
+        <v>0.69</v>
+      </c>
+      <c r="AR98">
+        <v>0.15</v>
+      </c>
+      <c r="AS98">
+        <v>429</v>
+      </c>
+      <c r="AT98">
+        <v>500</v>
+      </c>
+      <c r="AU98">
+        <v>239</v>
+      </c>
+      <c r="AV98">
+        <v>136</v>
+      </c>
+      <c r="AW98">
+        <v>114</v>
+      </c>
+      <c r="AX98">
+        <v>294</v>
+      </c>
+      <c r="AY98">
+        <v>25</v>
+      </c>
+      <c r="AZ98">
+        <v>19</v>
+      </c>
+      <c r="BA98">
+        <v>5</v>
+      </c>
+      <c r="BB98">
+        <v>7</v>
+      </c>
+      <c r="BC98">
+        <v>22</v>
+      </c>
+      <c r="BD98">
+        <v>13</v>
+      </c>
+      <c r="BE98">
+        <v>17</v>
+      </c>
+      <c r="BF98">
+        <v>34</v>
+      </c>
+      <c r="BG98">
+        <v>2</v>
+      </c>
+      <c r="BH98">
+        <v>0</v>
+      </c>
+      <c r="BI98" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ98" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK98">
+        <v>20</v>
+      </c>
+      <c r="BL98">
+        <v>21</v>
+      </c>
+      <c r="BM98">
+        <v>14</v>
+      </c>
+      <c r="BN98">
+        <v>5</v>
+      </c>
+      <c r="BO98">
+        <v>6</v>
+      </c>
+      <c r="BP98">
+        <v>2</v>
+      </c>
+      <c r="BQ98">
+        <v>41</v>
+      </c>
+      <c r="BR98">
+        <v>27</v>
+      </c>
+      <c r="BS98">
+        <v>2</v>
+      </c>
+      <c r="BT98">
+        <v>0</v>
+      </c>
+      <c r="BU98" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV98" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW98">
+        <v>45</v>
+      </c>
+      <c r="BX98">
+        <v>57</v>
+      </c>
+      <c r="BY98">
+        <v>36</v>
+      </c>
+      <c r="BZ98">
+        <v>44</v>
+      </c>
+      <c r="CA98">
+        <v>9</v>
+      </c>
+      <c r="CB98">
+        <v>13</v>
+      </c>
+      <c r="CC98">
+        <v>6</v>
+      </c>
+      <c r="CD98">
+        <v>5</v>
+      </c>
+      <c r="CE98" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF98" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG98">
+        <v>1</v>
+      </c>
+      <c r="CH98">
+        <v>1</v>
+      </c>
+      <c r="CI98">
+        <v>0</v>
+      </c>
+      <c r="CJ98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:88">
+      <c r="B99" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99">
+        <v>58</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I99">
+        <v>2.08</v>
+      </c>
+      <c r="J99">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K99">
+        <v>25</v>
+      </c>
+      <c r="L99">
+        <v>10</v>
+      </c>
+      <c r="M99">
+        <v>7</v>
+      </c>
+      <c r="N99">
+        <v>3</v>
+      </c>
+      <c r="O99">
+        <v>2</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="Q99">
+        <v>1</v>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="S99">
+        <v>404</v>
+      </c>
+      <c r="T99">
+        <v>282</v>
+      </c>
+      <c r="U99">
+        <v>8</v>
+      </c>
+      <c r="V99">
+        <v>5</v>
+      </c>
+      <c r="W99">
+        <v>8</v>
+      </c>
+      <c r="X99">
+        <v>2</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA99">
+        <v>12</v>
+      </c>
+      <c r="AB99">
+        <v>6</v>
+      </c>
+      <c r="AC99">
+        <v>6</v>
+      </c>
+      <c r="AD99">
+        <v>1</v>
+      </c>
+      <c r="AE99">
+        <v>0</v>
+      </c>
+      <c r="AF99">
+        <v>0</v>
+      </c>
+      <c r="AG99">
+        <v>11</v>
+      </c>
+      <c r="AH99">
+        <v>8</v>
+      </c>
+      <c r="AI99">
+        <v>14</v>
+      </c>
+      <c r="AJ99">
+        <v>2</v>
+      </c>
+      <c r="AK99">
+        <v>0.91</v>
+      </c>
+      <c r="AL99">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AM99">
+        <v>1.17</v>
+      </c>
+      <c r="AN99">
+        <v>0.27</v>
+      </c>
+      <c r="AO99">
+        <v>2.08</v>
+      </c>
+      <c r="AP99">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AQ99">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AR99">
+        <v>1.56</v>
+      </c>
+      <c r="AS99">
+        <v>489</v>
+      </c>
+      <c r="AT99">
+        <v>370</v>
+      </c>
+      <c r="AU99">
+        <v>168</v>
+      </c>
+      <c r="AV99">
+        <v>156</v>
+      </c>
+      <c r="AW99">
+        <v>236</v>
+      </c>
+      <c r="AX99">
+        <v>126</v>
+      </c>
+      <c r="AY99">
+        <v>21</v>
+      </c>
+      <c r="AZ99">
+        <v>28</v>
+      </c>
+      <c r="BA99">
+        <v>7</v>
+      </c>
+      <c r="BB99">
+        <v>3</v>
+      </c>
+      <c r="BC99">
+        <v>17</v>
+      </c>
+      <c r="BD99">
+        <v>19</v>
+      </c>
+      <c r="BE99">
+        <v>30</v>
+      </c>
+      <c r="BF99">
+        <v>17</v>
+      </c>
+      <c r="BG99">
+        <v>1</v>
+      </c>
+      <c r="BH99">
+        <v>4</v>
+      </c>
+      <c r="BI99" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ99" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK99">
+        <v>9</v>
+      </c>
+      <c r="BL99">
+        <v>14</v>
+      </c>
+      <c r="BM99">
+        <v>4</v>
+      </c>
+      <c r="BN99">
+        <v>8</v>
+      </c>
+      <c r="BO99">
+        <v>1</v>
+      </c>
+      <c r="BP99">
+        <v>6</v>
+      </c>
+      <c r="BQ99">
+        <v>19</v>
+      </c>
+      <c r="BR99">
+        <v>41</v>
+      </c>
+      <c r="BS99">
+        <v>1</v>
+      </c>
+      <c r="BT99">
+        <v>5</v>
+      </c>
+      <c r="BU99" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV99" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW99">
+        <v>43</v>
+      </c>
+      <c r="BX99">
+        <v>51</v>
+      </c>
+      <c r="BY99">
+        <v>17</v>
+      </c>
+      <c r="BZ99">
+        <v>28</v>
+      </c>
+      <c r="CA99">
+        <v>26</v>
+      </c>
+      <c r="CB99">
+        <v>23</v>
+      </c>
+      <c r="CC99">
+        <v>3</v>
+      </c>
+      <c r="CD99">
+        <v>7</v>
+      </c>
+      <c r="CE99" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF99" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG99">
+        <v>2</v>
+      </c>
+      <c r="CH99">
+        <v>2</v>
+      </c>
+      <c r="CI99">
+        <v>0</v>
+      </c>
+      <c r="CJ99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:88">
+      <c r="B100" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>52</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="I100">
+        <v>0.78</v>
+      </c>
+      <c r="J100">
+        <v>1.93</v>
+      </c>
+      <c r="K100">
+        <v>11</v>
+      </c>
+      <c r="L100">
+        <v>24</v>
+      </c>
+      <c r="M100">
+        <v>5</v>
+      </c>
+      <c r="N100">
+        <v>6</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>2</v>
+      </c>
+      <c r="Q100">
+        <v>1</v>
+      </c>
+      <c r="R100">
+        <v>2</v>
+      </c>
+      <c r="S100">
+        <v>400</v>
+      </c>
+      <c r="T100">
+        <v>364</v>
+      </c>
+      <c r="U100">
+        <v>17</v>
+      </c>
+      <c r="V100">
+        <v>16</v>
+      </c>
+      <c r="W100">
+        <v>4</v>
+      </c>
+      <c r="X100">
+        <v>7</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA100">
+        <v>3</v>
+      </c>
+      <c r="AB100">
+        <v>8</v>
+      </c>
+      <c r="AC100">
+        <v>3</v>
+      </c>
+      <c r="AD100">
+        <v>10</v>
+      </c>
+      <c r="AE100">
+        <v>0</v>
+      </c>
+      <c r="AF100">
+        <v>1</v>
+      </c>
+      <c r="AG100">
+        <v>8</v>
+      </c>
+      <c r="AH100">
+        <v>14</v>
+      </c>
+      <c r="AI100">
+        <v>3</v>
+      </c>
+      <c r="AJ100">
+        <v>10</v>
+      </c>
+      <c r="AK100">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AL100">
+        <v>1.67</v>
+      </c>
+      <c r="AM100">
+        <v>0.23</v>
+      </c>
+      <c r="AN100">
+        <v>0.25</v>
+      </c>
+      <c r="AO100">
+        <v>0.78</v>
+      </c>
+      <c r="AP100">
+        <v>1.93</v>
+      </c>
+      <c r="AQ100">
+        <v>0.45</v>
+      </c>
+      <c r="AR100">
+        <v>1.55</v>
+      </c>
+      <c r="AS100">
+        <v>477</v>
+      </c>
+      <c r="AT100">
+        <v>441</v>
+      </c>
+      <c r="AU100">
+        <v>202</v>
+      </c>
+      <c r="AV100">
+        <v>180</v>
+      </c>
+      <c r="AW100">
+        <v>198</v>
+      </c>
+      <c r="AX100">
+        <v>184</v>
+      </c>
+      <c r="AY100">
+        <v>31</v>
+      </c>
+      <c r="AZ100">
+        <v>29</v>
+      </c>
+      <c r="BA100">
+        <v>6</v>
+      </c>
+      <c r="BB100">
+        <v>5</v>
+      </c>
+      <c r="BC100">
+        <v>16</v>
+      </c>
+      <c r="BD100">
+        <v>18</v>
+      </c>
+      <c r="BE100">
+        <v>16</v>
+      </c>
+      <c r="BF100">
+        <v>42</v>
+      </c>
+      <c r="BG100">
+        <v>1</v>
+      </c>
+      <c r="BH100">
+        <v>2</v>
+      </c>
+      <c r="BI100" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ100" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK100">
+        <v>26</v>
+      </c>
+      <c r="BL100">
+        <v>18</v>
+      </c>
+      <c r="BM100">
+        <v>12</v>
+      </c>
+      <c r="BN100">
+        <v>6</v>
+      </c>
+      <c r="BO100">
+        <v>9</v>
+      </c>
+      <c r="BP100">
+        <v>3</v>
+      </c>
+      <c r="BQ100">
+        <v>31</v>
+      </c>
+      <c r="BR100">
+        <v>27</v>
+      </c>
+      <c r="BS100">
+        <v>5</v>
+      </c>
+      <c r="BT100">
+        <v>4</v>
+      </c>
+      <c r="BU100" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV100" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW100">
+        <v>69</v>
+      </c>
+      <c r="BX100">
+        <v>53</v>
+      </c>
+      <c r="BY100">
+        <v>49</v>
+      </c>
+      <c r="BZ100">
+        <v>40</v>
+      </c>
+      <c r="CA100">
+        <v>20</v>
+      </c>
+      <c r="CB100">
+        <v>13</v>
+      </c>
+      <c r="CC100">
+        <v>7</v>
+      </c>
+      <c r="CD100">
+        <v>6</v>
+      </c>
+      <c r="CE100" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF100" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG100">
+        <v>2</v>
+      </c>
+      <c r="CH100">
+        <v>1</v>
+      </c>
+      <c r="CI100">
+        <v>0</v>
+      </c>
+      <c r="CJ100">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A341ED-5BE6-4409-92E8-DDDC89C47253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB400B8-2807-4B8F-9F0C-5D4BB1030587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="208">
   <si>
     <t>date</t>
   </si>
@@ -652,6 +652,18 @@
   <si>
     <t>Fri 23 October, 20:30</t>
   </si>
+  <si>
+    <t>Sat 24 October, 12:15</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 14:45</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 17:30</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 20:15</t>
+  </si>
 </sst>
 </file>
 
@@ -706,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -727,6 +739,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ100"/>
+  <dimension ref="A1:CJ104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1397,7 +1412,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H100" si="0">100-G2</f>
+        <f t="shared" ref="H2:H104" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -24603,7 +24618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:88" ht="30">
+    <row r="89" spans="1:88" ht="31.5" customHeight="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -27795,6 +27810,1062 @@
         <v>0</v>
       </c>
       <c r="CJ100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:88" ht="16.5" customHeight="1">
+      <c r="B101" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C101" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" t="s">
+        <v>102</v>
+      </c>
+      <c r="E101">
+        <v>3</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>55</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="I101">
+        <v>1.7</v>
+      </c>
+      <c r="J101">
+        <v>1.48</v>
+      </c>
+      <c r="K101">
+        <v>18</v>
+      </c>
+      <c r="L101">
+        <v>13</v>
+      </c>
+      <c r="M101">
+        <v>7</v>
+      </c>
+      <c r="N101">
+        <v>5</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="P101">
+        <v>3</v>
+      </c>
+      <c r="Q101">
+        <v>1</v>
+      </c>
+      <c r="R101">
+        <v>2</v>
+      </c>
+      <c r="S101">
+        <v>424</v>
+      </c>
+      <c r="T101">
+        <v>315</v>
+      </c>
+      <c r="U101">
+        <v>8</v>
+      </c>
+      <c r="V101">
+        <v>11</v>
+      </c>
+      <c r="W101">
+        <v>4</v>
+      </c>
+      <c r="X101">
+        <v>4</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA101">
+        <v>4</v>
+      </c>
+      <c r="AB101">
+        <v>5</v>
+      </c>
+      <c r="AC101">
+        <v>7</v>
+      </c>
+      <c r="AD101">
+        <v>3</v>
+      </c>
+      <c r="AE101">
+        <v>0</v>
+      </c>
+      <c r="AF101">
+        <v>0</v>
+      </c>
+      <c r="AG101">
+        <v>11</v>
+      </c>
+      <c r="AH101">
+        <v>7</v>
+      </c>
+      <c r="AI101">
+        <v>7</v>
+      </c>
+      <c r="AJ101">
+        <v>6</v>
+      </c>
+      <c r="AK101">
+        <v>1.57</v>
+      </c>
+      <c r="AL101">
+        <v>1.41</v>
+      </c>
+      <c r="AM101">
+        <v>0.12</v>
+      </c>
+      <c r="AN101">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AO101">
+        <v>1.7</v>
+      </c>
+      <c r="AP101">
+        <v>1.48</v>
+      </c>
+      <c r="AQ101">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AR101">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AS101">
+        <v>495</v>
+      </c>
+      <c r="AT101">
+        <v>385</v>
+      </c>
+      <c r="AU101">
+        <v>262</v>
+      </c>
+      <c r="AV101">
+        <v>112</v>
+      </c>
+      <c r="AW101">
+        <v>162</v>
+      </c>
+      <c r="AX101">
+        <v>203</v>
+      </c>
+      <c r="AY101">
+        <v>15</v>
+      </c>
+      <c r="AZ101">
+        <v>22</v>
+      </c>
+      <c r="BA101">
+        <v>3</v>
+      </c>
+      <c r="BB101">
+        <v>6</v>
+      </c>
+      <c r="BC101">
+        <v>11</v>
+      </c>
+      <c r="BD101">
+        <v>14</v>
+      </c>
+      <c r="BE101">
+        <v>31</v>
+      </c>
+      <c r="BF101">
+        <v>26</v>
+      </c>
+      <c r="BG101">
+        <v>0</v>
+      </c>
+      <c r="BH101">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ101" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK101">
+        <v>8</v>
+      </c>
+      <c r="BL101">
+        <v>20</v>
+      </c>
+      <c r="BM101">
+        <v>8</v>
+      </c>
+      <c r="BN101">
+        <v>3</v>
+      </c>
+      <c r="BO101">
+        <v>3</v>
+      </c>
+      <c r="BP101">
+        <v>7</v>
+      </c>
+      <c r="BQ101">
+        <v>30</v>
+      </c>
+      <c r="BR101">
+        <v>16</v>
+      </c>
+      <c r="BS101">
+        <v>4</v>
+      </c>
+      <c r="BT101">
+        <v>3</v>
+      </c>
+      <c r="BU101" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV101" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW101">
+        <v>37</v>
+      </c>
+      <c r="BX101">
+        <v>37</v>
+      </c>
+      <c r="BY101">
+        <v>24</v>
+      </c>
+      <c r="BZ101">
+        <v>28</v>
+      </c>
+      <c r="CA101">
+        <v>13</v>
+      </c>
+      <c r="CB101">
+        <v>9</v>
+      </c>
+      <c r="CC101">
+        <v>6</v>
+      </c>
+      <c r="CD101">
+        <v>1</v>
+      </c>
+      <c r="CE101" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF101" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG101">
+        <v>3</v>
+      </c>
+      <c r="CH101">
+        <v>2</v>
+      </c>
+      <c r="CI101">
+        <v>0</v>
+      </c>
+      <c r="CJ101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:88">
+      <c r="B102" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C102" t="s">
+        <v>96</v>
+      </c>
+      <c r="D102" t="s">
+        <v>111</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>47</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="I102">
+        <v>1.07</v>
+      </c>
+      <c r="J102">
+        <v>1.87</v>
+      </c>
+      <c r="K102">
+        <v>16</v>
+      </c>
+      <c r="L102">
+        <v>8</v>
+      </c>
+      <c r="M102">
+        <v>7</v>
+      </c>
+      <c r="N102">
+        <v>2</v>
+      </c>
+      <c r="O102">
+        <v>2</v>
+      </c>
+      <c r="P102">
+        <v>2</v>
+      </c>
+      <c r="Q102">
+        <v>2</v>
+      </c>
+      <c r="R102">
+        <v>2</v>
+      </c>
+      <c r="S102">
+        <v>288</v>
+      </c>
+      <c r="T102">
+        <v>346</v>
+      </c>
+      <c r="U102">
+        <v>10</v>
+      </c>
+      <c r="V102">
+        <v>19</v>
+      </c>
+      <c r="W102">
+        <v>9</v>
+      </c>
+      <c r="X102">
+        <v>4</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA102">
+        <v>6</v>
+      </c>
+      <c r="AB102">
+        <v>4</v>
+      </c>
+      <c r="AC102">
+        <v>3</v>
+      </c>
+      <c r="AD102">
+        <v>2</v>
+      </c>
+      <c r="AE102">
+        <v>0</v>
+      </c>
+      <c r="AF102">
+        <v>0</v>
+      </c>
+      <c r="AG102">
+        <v>10</v>
+      </c>
+      <c r="AH102">
+        <v>7</v>
+      </c>
+      <c r="AI102">
+        <v>6</v>
+      </c>
+      <c r="AJ102">
+        <v>1</v>
+      </c>
+      <c r="AK102">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AL102">
+        <v>0.73</v>
+      </c>
+      <c r="AM102">
+        <v>0.49</v>
+      </c>
+      <c r="AN102">
+        <v>0.35</v>
+      </c>
+      <c r="AO102">
+        <v>1.07</v>
+      </c>
+      <c r="AP102">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AQ102">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AR102">
+        <v>1.02</v>
+      </c>
+      <c r="AS102">
+        <v>367</v>
+      </c>
+      <c r="AT102">
+        <v>431</v>
+      </c>
+      <c r="AU102">
+        <v>156</v>
+      </c>
+      <c r="AV102">
+        <v>204</v>
+      </c>
+      <c r="AW102">
+        <v>132</v>
+      </c>
+      <c r="AX102">
+        <v>142</v>
+      </c>
+      <c r="AY102">
+        <v>22</v>
+      </c>
+      <c r="AZ102">
+        <v>18</v>
+      </c>
+      <c r="BA102">
+        <v>3</v>
+      </c>
+      <c r="BB102">
+        <v>2</v>
+      </c>
+      <c r="BC102">
+        <v>12</v>
+      </c>
+      <c r="BD102">
+        <v>16</v>
+      </c>
+      <c r="BE102">
+        <v>21</v>
+      </c>
+      <c r="BF102">
+        <v>32</v>
+      </c>
+      <c r="BG102">
+        <v>6</v>
+      </c>
+      <c r="BH102">
+        <v>0</v>
+      </c>
+      <c r="BI102" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ102" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK102">
+        <v>20</v>
+      </c>
+      <c r="BL102">
+        <v>17</v>
+      </c>
+      <c r="BM102">
+        <v>7</v>
+      </c>
+      <c r="BN102">
+        <v>6</v>
+      </c>
+      <c r="BO102">
+        <v>2</v>
+      </c>
+      <c r="BP102">
+        <v>4</v>
+      </c>
+      <c r="BQ102">
+        <v>24</v>
+      </c>
+      <c r="BR102">
+        <v>38</v>
+      </c>
+      <c r="BS102">
+        <v>2</v>
+      </c>
+      <c r="BT102">
+        <v>5</v>
+      </c>
+      <c r="BU102" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV102" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW102">
+        <v>55</v>
+      </c>
+      <c r="BX102">
+        <v>38</v>
+      </c>
+      <c r="BY102">
+        <v>42</v>
+      </c>
+      <c r="BZ102">
+        <v>29</v>
+      </c>
+      <c r="CA102">
+        <v>13</v>
+      </c>
+      <c r="CB102">
+        <v>9</v>
+      </c>
+      <c r="CC102">
+        <v>3</v>
+      </c>
+      <c r="CD102">
+        <v>3</v>
+      </c>
+      <c r="CE102" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF102" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG102">
+        <v>2</v>
+      </c>
+      <c r="CH102">
+        <v>4</v>
+      </c>
+      <c r="CI102">
+        <v>0</v>
+      </c>
+      <c r="CJ102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:88" ht="30">
+      <c r="B103" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E103">
+        <v>4</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103">
+        <v>53</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I103">
+        <v>1.02</v>
+      </c>
+      <c r="J103">
+        <v>1.94</v>
+      </c>
+      <c r="K103">
+        <v>9</v>
+      </c>
+      <c r="L103">
+        <v>16</v>
+      </c>
+      <c r="M103">
+        <v>5</v>
+      </c>
+      <c r="N103">
+        <v>5</v>
+      </c>
+      <c r="O103">
+        <v>3</v>
+      </c>
+      <c r="P103">
+        <v>3</v>
+      </c>
+      <c r="Q103">
+        <v>1</v>
+      </c>
+      <c r="R103">
+        <v>1</v>
+      </c>
+      <c r="S103">
+        <v>397</v>
+      </c>
+      <c r="T103">
+        <v>332</v>
+      </c>
+      <c r="U103">
+        <v>14</v>
+      </c>
+      <c r="V103">
+        <v>7</v>
+      </c>
+      <c r="W103">
+        <v>2</v>
+      </c>
+      <c r="X103">
+        <v>7</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA103">
+        <v>3</v>
+      </c>
+      <c r="AB103">
+        <v>8</v>
+      </c>
+      <c r="AC103">
+        <v>1</v>
+      </c>
+      <c r="AD103">
+        <v>3</v>
+      </c>
+      <c r="AE103">
+        <v>0</v>
+      </c>
+      <c r="AF103">
+        <v>0</v>
+      </c>
+      <c r="AG103">
+        <v>6</v>
+      </c>
+      <c r="AH103">
+        <v>10</v>
+      </c>
+      <c r="AI103">
+        <v>3</v>
+      </c>
+      <c r="AJ103">
+        <v>6</v>
+      </c>
+      <c r="AK103">
+        <v>0.78</v>
+      </c>
+      <c r="AL103">
+        <v>0.87</v>
+      </c>
+      <c r="AM103">
+        <v>0.24</v>
+      </c>
+      <c r="AN103">
+        <v>0.27</v>
+      </c>
+      <c r="AO103">
+        <v>1.02</v>
+      </c>
+      <c r="AP103">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AQ103">
+        <v>1.45</v>
+      </c>
+      <c r="AR103">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AS103">
+        <v>460</v>
+      </c>
+      <c r="AT103">
+        <v>397</v>
+      </c>
+      <c r="AU103">
+        <v>199</v>
+      </c>
+      <c r="AV103">
+        <v>184</v>
+      </c>
+      <c r="AW103">
+        <v>198</v>
+      </c>
+      <c r="AX103">
+        <v>148</v>
+      </c>
+      <c r="AY103">
+        <v>29</v>
+      </c>
+      <c r="AZ103">
+        <v>13</v>
+      </c>
+      <c r="BA103">
+        <v>2</v>
+      </c>
+      <c r="BB103">
+        <v>3</v>
+      </c>
+      <c r="BC103">
+        <v>23</v>
+      </c>
+      <c r="BD103">
+        <v>16</v>
+      </c>
+      <c r="BE103">
+        <v>20</v>
+      </c>
+      <c r="BF103">
+        <v>25</v>
+      </c>
+      <c r="BG103">
+        <v>3</v>
+      </c>
+      <c r="BH103">
+        <v>2</v>
+      </c>
+      <c r="BI103" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ103" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK103">
+        <v>15</v>
+      </c>
+      <c r="BL103">
+        <v>23</v>
+      </c>
+      <c r="BM103">
+        <v>10</v>
+      </c>
+      <c r="BN103">
+        <v>5</v>
+      </c>
+      <c r="BO103">
+        <v>3</v>
+      </c>
+      <c r="BP103">
+        <v>1</v>
+      </c>
+      <c r="BQ103">
+        <v>36</v>
+      </c>
+      <c r="BR103">
+        <v>41</v>
+      </c>
+      <c r="BS103">
+        <v>2</v>
+      </c>
+      <c r="BT103">
+        <v>1</v>
+      </c>
+      <c r="BU103" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV103" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW103">
+        <v>50</v>
+      </c>
+      <c r="BX103">
+        <v>56</v>
+      </c>
+      <c r="BY103">
+        <v>29</v>
+      </c>
+      <c r="BZ103">
+        <v>46</v>
+      </c>
+      <c r="CA103">
+        <v>21</v>
+      </c>
+      <c r="CB103">
+        <v>10</v>
+      </c>
+      <c r="CC103">
+        <v>9</v>
+      </c>
+      <c r="CD103">
+        <v>10</v>
+      </c>
+      <c r="CE103" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF103" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG103">
+        <v>2</v>
+      </c>
+      <c r="CH103">
+        <v>0</v>
+      </c>
+      <c r="CI103">
+        <v>0</v>
+      </c>
+      <c r="CJ103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:88" ht="30">
+      <c r="B104" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>58</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I104">
+        <v>1.01</v>
+      </c>
+      <c r="J104">
+        <v>1.95</v>
+      </c>
+      <c r="K104">
+        <v>13</v>
+      </c>
+      <c r="L104">
+        <v>13</v>
+      </c>
+      <c r="M104">
+        <v>8</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
+      <c r="P104">
+        <v>2</v>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="R104">
+        <v>1</v>
+      </c>
+      <c r="S104">
+        <v>440</v>
+      </c>
+      <c r="T104">
+        <v>305</v>
+      </c>
+      <c r="U104">
+        <v>13</v>
+      </c>
+      <c r="V104">
+        <v>6</v>
+      </c>
+      <c r="W104">
+        <v>1</v>
+      </c>
+      <c r="X104">
+        <v>4</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA104">
+        <v>3</v>
+      </c>
+      <c r="AB104">
+        <v>7</v>
+      </c>
+      <c r="AC104">
+        <v>2</v>
+      </c>
+      <c r="AD104">
+        <v>4</v>
+      </c>
+      <c r="AE104">
+        <v>0</v>
+      </c>
+      <c r="AF104">
+        <v>0</v>
+      </c>
+      <c r="AG104">
+        <v>8</v>
+      </c>
+      <c r="AH104">
+        <v>10</v>
+      </c>
+      <c r="AI104">
+        <v>5</v>
+      </c>
+      <c r="AJ104">
+        <v>3</v>
+      </c>
+      <c r="AK104">
+        <v>0.83</v>
+      </c>
+      <c r="AL104">
+        <v>0.51</v>
+      </c>
+      <c r="AM104">
+        <v>0.19</v>
+      </c>
+      <c r="AN104">
+        <v>0.66</v>
+      </c>
+      <c r="AO104">
+        <v>1.01</v>
+      </c>
+      <c r="AP104">
+        <v>1.17</v>
+      </c>
+      <c r="AQ104">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AR104">
+        <v>1.33</v>
+      </c>
+      <c r="AS104">
+        <v>535</v>
+      </c>
+      <c r="AT104">
+        <v>375</v>
+      </c>
+      <c r="AU104">
+        <v>174</v>
+      </c>
+      <c r="AV104">
+        <v>144</v>
+      </c>
+      <c r="AW104">
+        <v>266</v>
+      </c>
+      <c r="AX104">
+        <v>161</v>
+      </c>
+      <c r="AY104">
+        <v>17</v>
+      </c>
+      <c r="AZ104">
+        <v>21</v>
+      </c>
+      <c r="BA104">
+        <v>2</v>
+      </c>
+      <c r="BB104">
+        <v>5</v>
+      </c>
+      <c r="BC104">
+        <v>19</v>
+      </c>
+      <c r="BD104">
+        <v>12</v>
+      </c>
+      <c r="BE104">
+        <v>25</v>
+      </c>
+      <c r="BF104">
+        <v>22</v>
+      </c>
+      <c r="BG104">
+        <v>2</v>
+      </c>
+      <c r="BH104">
+        <v>2</v>
+      </c>
+      <c r="BI104" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ104" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK104">
+        <v>18</v>
+      </c>
+      <c r="BL104">
+        <v>22</v>
+      </c>
+      <c r="BM104">
+        <v>7</v>
+      </c>
+      <c r="BN104">
+        <v>16</v>
+      </c>
+      <c r="BO104">
+        <v>4</v>
+      </c>
+      <c r="BP104">
+        <v>2</v>
+      </c>
+      <c r="BQ104">
+        <v>15</v>
+      </c>
+      <c r="BR104">
+        <v>25</v>
+      </c>
+      <c r="BS104">
+        <v>1</v>
+      </c>
+      <c r="BT104">
+        <v>6</v>
+      </c>
+      <c r="BU104" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV104" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW104">
+        <v>43</v>
+      </c>
+      <c r="BX104">
+        <v>62</v>
+      </c>
+      <c r="BY104">
+        <v>31</v>
+      </c>
+      <c r="BZ104">
+        <v>46</v>
+      </c>
+      <c r="CA104">
+        <v>12</v>
+      </c>
+      <c r="CB104">
+        <v>16</v>
+      </c>
+      <c r="CC104">
+        <v>7</v>
+      </c>
+      <c r="CD104">
+        <v>12</v>
+      </c>
+      <c r="CE104" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF104" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG104">
+        <v>0</v>
+      </c>
+      <c r="CH104">
+        <v>2</v>
+      </c>
+      <c r="CI104">
+        <v>0</v>
+      </c>
+      <c r="CJ104">
         <v>0</v>
       </c>
     </row>

--- a/Ekstraklasa 2026-2027.xlsx
+++ b/Ekstraklasa 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB400B8-2807-4B8F-9F0C-5D4BB1030587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{244761C7-690C-4D83-ABBA-DD84F11FF902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2135F1F7-09EA-48F3-B6CC-5B3344B37E4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="211">
   <si>
     <t>date</t>
   </si>
@@ -664,6 +664,15 @@
   <si>
     <t>Sat 24 October, 20:15</t>
   </si>
+  <si>
+    <t>Sun 25 October, 12:15</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 14:45</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 17:30</t>
+  </si>
 </sst>
 </file>
 
@@ -718,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -742,6 +751,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1077,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2594D30A-B571-44E9-871B-38CB8D593531}">
-  <dimension ref="A1:CJ104"/>
+  <dimension ref="A1:CJ107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1412,7 +1427,7 @@
         <v>42</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H104" si="0">100-G2</f>
+        <f t="shared" ref="H2:H107" si="0">100-G2</f>
         <v>58</v>
       </c>
       <c r="I2" s="3">
@@ -28866,6 +28881,798 @@
         <v>0</v>
       </c>
       <c r="CJ104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:88" ht="29.25" customHeight="1">
+      <c r="B105" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" t="s">
+        <v>99</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>40</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I105">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="J105">
+        <v>1.57</v>
+      </c>
+      <c r="K105">
+        <v>15</v>
+      </c>
+      <c r="L105">
+        <v>16</v>
+      </c>
+      <c r="M105">
+        <v>4</v>
+      </c>
+      <c r="N105">
+        <v>4</v>
+      </c>
+      <c r="O105">
+        <v>4</v>
+      </c>
+      <c r="P105">
+        <v>2</v>
+      </c>
+      <c r="Q105">
+        <v>3</v>
+      </c>
+      <c r="R105">
+        <v>2</v>
+      </c>
+      <c r="S105">
+        <v>316</v>
+      </c>
+      <c r="T105">
+        <v>498</v>
+      </c>
+      <c r="U105">
+        <v>8</v>
+      </c>
+      <c r="V105">
+        <v>9</v>
+      </c>
+      <c r="W105">
+        <v>4</v>
+      </c>
+      <c r="X105">
+        <v>7</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA105">
+        <v>9</v>
+      </c>
+      <c r="AB105">
+        <v>8</v>
+      </c>
+      <c r="AC105">
+        <v>2</v>
+      </c>
+      <c r="AD105">
+        <v>4</v>
+      </c>
+      <c r="AE105">
+        <v>0</v>
+      </c>
+      <c r="AF105">
+        <v>0</v>
+      </c>
+      <c r="AG105">
+        <v>8</v>
+      </c>
+      <c r="AH105">
+        <v>11</v>
+      </c>
+      <c r="AI105">
+        <v>7</v>
+      </c>
+      <c r="AJ105">
+        <v>5</v>
+      </c>
+      <c r="AK105">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AL105">
+        <v>1.34</v>
+      </c>
+      <c r="AM105">
+        <v>0.21</v>
+      </c>
+      <c r="AN105">
+        <v>0.23</v>
+      </c>
+      <c r="AO105">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AP105">
+        <v>1.57</v>
+      </c>
+      <c r="AQ105">
+        <v>1.21</v>
+      </c>
+      <c r="AR105">
+        <v>1</v>
+      </c>
+      <c r="AS105">
+        <v>392</v>
+      </c>
+      <c r="AT105">
+        <v>589</v>
+      </c>
+      <c r="AU105">
+        <v>155</v>
+      </c>
+      <c r="AV105">
+        <v>209</v>
+      </c>
+      <c r="AW105">
+        <v>161</v>
+      </c>
+      <c r="AX105">
+        <v>289</v>
+      </c>
+      <c r="AY105">
+        <v>28</v>
+      </c>
+      <c r="AZ105">
+        <v>15</v>
+      </c>
+      <c r="BA105">
+        <v>0</v>
+      </c>
+      <c r="BB105">
+        <v>11</v>
+      </c>
+      <c r="BC105">
+        <v>20</v>
+      </c>
+      <c r="BD105">
+        <v>21</v>
+      </c>
+      <c r="BE105">
+        <v>23</v>
+      </c>
+      <c r="BF105">
+        <v>36</v>
+      </c>
+      <c r="BG105">
+        <v>5</v>
+      </c>
+      <c r="BH105">
+        <v>0</v>
+      </c>
+      <c r="BI105" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ105" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK105">
+        <v>14</v>
+      </c>
+      <c r="BL105">
+        <v>15</v>
+      </c>
+      <c r="BM105">
+        <v>6</v>
+      </c>
+      <c r="BN105">
+        <v>13</v>
+      </c>
+      <c r="BO105">
+        <v>4</v>
+      </c>
+      <c r="BP105">
+        <v>2</v>
+      </c>
+      <c r="BQ105">
+        <v>26</v>
+      </c>
+      <c r="BR105">
+        <v>14</v>
+      </c>
+      <c r="BS105">
+        <v>4</v>
+      </c>
+      <c r="BT105">
+        <v>2</v>
+      </c>
+      <c r="BU105" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV105" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW105">
+        <v>36</v>
+      </c>
+      <c r="BX105">
+        <v>36</v>
+      </c>
+      <c r="BY105">
+        <v>30</v>
+      </c>
+      <c r="BZ105">
+        <v>25</v>
+      </c>
+      <c r="CA105">
+        <v>6</v>
+      </c>
+      <c r="CB105">
+        <v>11</v>
+      </c>
+      <c r="CC105">
+        <v>8</v>
+      </c>
+      <c r="CD105">
+        <v>3</v>
+      </c>
+      <c r="CE105" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF105" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG105">
+        <v>3</v>
+      </c>
+      <c r="CH105">
+        <v>2</v>
+      </c>
+      <c r="CI105">
+        <v>0</v>
+      </c>
+      <c r="CJ105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:88" ht="30">
+      <c r="B106" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D106" t="s">
+        <v>105</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>53</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I106">
+        <v>2.23</v>
+      </c>
+      <c r="J106">
+        <v>0.63</v>
+      </c>
+      <c r="K106">
+        <v>21</v>
+      </c>
+      <c r="L106">
+        <v>7</v>
+      </c>
+      <c r="M106">
+        <v>4</v>
+      </c>
+      <c r="N106">
+        <v>4</v>
+      </c>
+      <c r="O106">
+        <v>2</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>1</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <v>401</v>
+      </c>
+      <c r="T106">
+        <v>333</v>
+      </c>
+      <c r="U106">
+        <v>16</v>
+      </c>
+      <c r="V106">
+        <v>12</v>
+      </c>
+      <c r="W106">
+        <v>8</v>
+      </c>
+      <c r="X106">
+        <v>3</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA106">
+        <v>7</v>
+      </c>
+      <c r="AB106">
+        <v>2</v>
+      </c>
+      <c r="AC106">
+        <v>10</v>
+      </c>
+      <c r="AD106">
+        <v>1</v>
+      </c>
+      <c r="AE106">
+        <v>0</v>
+      </c>
+      <c r="AF106">
+        <v>0</v>
+      </c>
+      <c r="AG106">
+        <v>13</v>
+      </c>
+      <c r="AH106">
+        <v>6</v>
+      </c>
+      <c r="AI106">
+        <v>8</v>
+      </c>
+      <c r="AJ106">
+        <v>1</v>
+      </c>
+      <c r="AK106">
+        <v>2.02</v>
+      </c>
+      <c r="AL106">
+        <v>0.63</v>
+      </c>
+      <c r="AM106">
+        <v>0.2</v>
+      </c>
+      <c r="AN106">
+        <v>0</v>
+      </c>
+      <c r="AO106">
+        <v>2.23</v>
+      </c>
+      <c r="AP106">
+        <v>0.63</v>
+      </c>
+      <c r="AQ106">
+        <v>1.04</v>
+      </c>
+      <c r="AR106">
+        <v>1.07</v>
+      </c>
+      <c r="AS106">
+        <v>481</v>
+      </c>
+      <c r="AT106">
+        <v>428</v>
+      </c>
+      <c r="AU106">
+        <v>161</v>
+      </c>
+      <c r="AV106">
+        <v>198</v>
+      </c>
+      <c r="AW106">
+        <v>240</v>
+      </c>
+      <c r="AX106">
+        <v>135</v>
+      </c>
+      <c r="AY106">
+        <v>25</v>
+      </c>
+      <c r="AZ106">
+        <v>24</v>
+      </c>
+      <c r="BA106">
+        <v>7</v>
+      </c>
+      <c r="BB106">
+        <v>1</v>
+      </c>
+      <c r="BC106">
+        <v>22</v>
+      </c>
+      <c r="BD106">
+        <v>19</v>
+      </c>
+      <c r="BE106">
+        <v>39</v>
+      </c>
+      <c r="BF106">
+        <v>14</v>
+      </c>
+      <c r="BG106">
+        <v>2</v>
+      </c>
+      <c r="BH106">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ106" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK106">
+        <v>21</v>
+      </c>
+      <c r="BL106">
+        <v>19</v>
+      </c>
+      <c r="BM106">
+        <v>10</v>
+      </c>
+      <c r="BN106">
+        <v>10</v>
+      </c>
+      <c r="BO106">
+        <v>1</v>
+      </c>
+      <c r="BP106">
+        <v>11</v>
+      </c>
+      <c r="BQ106">
+        <v>26</v>
+      </c>
+      <c r="BR106">
+        <v>26</v>
+      </c>
+      <c r="BS106">
+        <v>4</v>
+      </c>
+      <c r="BT106">
+        <v>2</v>
+      </c>
+      <c r="BU106" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV106" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW106">
+        <v>64</v>
+      </c>
+      <c r="BX106">
+        <v>45</v>
+      </c>
+      <c r="BY106">
+        <v>48</v>
+      </c>
+      <c r="BZ106">
+        <v>40</v>
+      </c>
+      <c r="CA106">
+        <v>16</v>
+      </c>
+      <c r="CB106">
+        <v>5</v>
+      </c>
+      <c r="CC106">
+        <v>15</v>
+      </c>
+      <c r="CD106">
+        <v>5</v>
+      </c>
+      <c r="CE106" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF106" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG106">
+        <v>0</v>
+      </c>
+      <c r="CH106">
+        <v>0</v>
+      </c>
+      <c r="CI106">
+        <v>0</v>
+      </c>
+      <c r="CJ106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:88" ht="30">
+      <c r="B107" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107">
+        <v>56</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="I107">
+        <v>1.46</v>
+      </c>
+      <c r="J107">
+        <v>1.25</v>
+      </c>
+      <c r="K107">
+        <v>17</v>
+      </c>
+      <c r="L107">
+        <v>10</v>
+      </c>
+      <c r="M107">
+        <v>9</v>
+      </c>
+      <c r="N107">
+        <v>5</v>
+      </c>
+      <c r="O107">
+        <v>4</v>
+      </c>
+      <c r="P107">
+        <v>2</v>
+      </c>
+      <c r="Q107">
+        <v>3</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>402</v>
+      </c>
+      <c r="T107">
+        <v>308</v>
+      </c>
+      <c r="U107">
+        <v>15</v>
+      </c>
+      <c r="V107">
+        <v>12</v>
+      </c>
+      <c r="W107">
+        <v>9</v>
+      </c>
+      <c r="X107">
+        <v>5</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA107">
+        <v>4</v>
+      </c>
+      <c r="AB107">
+        <v>3</v>
+      </c>
+      <c r="AC107">
+        <v>4</v>
+      </c>
+      <c r="AD107">
+        <v>2</v>
+      </c>
+      <c r="AE107">
+        <v>1</v>
+      </c>
+      <c r="AF107">
+        <v>1</v>
+      </c>
+      <c r="AG107">
+        <v>11</v>
+      </c>
+      <c r="AH107">
+        <v>6</v>
+      </c>
+      <c r="AI107">
+        <v>6</v>
+      </c>
+      <c r="AJ107">
+        <v>4</v>
+      </c>
+      <c r="AK107">
+        <v>0.72</v>
+      </c>
+      <c r="AL107">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AM107">
+        <v>0.75</v>
+      </c>
+      <c r="AN107">
+        <v>0.13</v>
+      </c>
+      <c r="AO107">
+        <v>1.46</v>
+      </c>
+      <c r="AP107">
+        <v>1.25</v>
+      </c>
+      <c r="AQ107">
+        <v>2.04</v>
+      </c>
+      <c r="AR107">
+        <v>2.08</v>
+      </c>
+      <c r="AS107">
+        <v>475</v>
+      </c>
+      <c r="AT107">
+        <v>380</v>
+      </c>
+      <c r="AU107">
+        <v>214</v>
+      </c>
+      <c r="AV107">
+        <v>174</v>
+      </c>
+      <c r="AW107">
+        <v>188</v>
+      </c>
+      <c r="AX107">
+        <v>134</v>
+      </c>
+      <c r="AY107">
+        <v>26</v>
+      </c>
+      <c r="AZ107">
+        <v>15</v>
+      </c>
+      <c r="BA107">
+        <v>6</v>
+      </c>
+      <c r="BB107">
+        <v>2</v>
+      </c>
+      <c r="BC107">
+        <v>15</v>
+      </c>
+      <c r="BD107">
+        <v>11</v>
+      </c>
+      <c r="BE107">
+        <v>29</v>
+      </c>
+      <c r="BF107">
+        <v>20</v>
+      </c>
+      <c r="BG107">
+        <v>2</v>
+      </c>
+      <c r="BH107">
+        <v>0</v>
+      </c>
+      <c r="BI107" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ107" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK107">
+        <v>10</v>
+      </c>
+      <c r="BL107">
+        <v>14</v>
+      </c>
+      <c r="BM107">
+        <v>13</v>
+      </c>
+      <c r="BN107">
+        <v>9</v>
+      </c>
+      <c r="BO107">
+        <v>3</v>
+      </c>
+      <c r="BP107">
+        <v>4</v>
+      </c>
+      <c r="BQ107">
+        <v>11</v>
+      </c>
+      <c r="BR107">
+        <v>35</v>
+      </c>
+      <c r="BS107">
+        <v>2</v>
+      </c>
+      <c r="BT107">
+        <v>8</v>
+      </c>
+      <c r="BU107" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV107" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW107">
+        <v>38</v>
+      </c>
+      <c r="BX107">
+        <v>49</v>
+      </c>
+      <c r="BY107">
+        <v>30</v>
+      </c>
+      <c r="BZ107">
+        <v>43</v>
+      </c>
+      <c r="CA107">
+        <v>8</v>
+      </c>
+      <c r="CB107">
+        <v>6</v>
+      </c>
+      <c r="CC107">
+        <v>8</v>
+      </c>
+      <c r="CD107">
+        <v>15</v>
+      </c>
+      <c r="CE107" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF107" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG107">
+        <v>2</v>
+      </c>
+      <c r="CH107">
+        <v>2</v>
+      </c>
+      <c r="CI107">
+        <v>0</v>
+      </c>
+      <c r="CJ107">
         <v>0</v>
       </c>
     </row>
